--- a/template.xlsx
+++ b/template.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -21,7 +21,7 @@
     <sheet name="이미인" sheetId="18" r:id="rId6"/>
     <sheet name="코스메카코리아" sheetId="19" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -33,6 +33,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="37">
   <si>
     <t>순번</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -82,46 +84,6 @@
   <si>
     <t>인사총무팀</t>
     <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>셀바이오휴먼텍</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026.10.04</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026.10.05</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>적합 예시</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>부적합 예시</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>셀바이오휴먼텍, 화성 2공장 준공을 통해 여드름 패치용 하이드로콜로이드 생산능력을 2배 확대하고 하이드로겔 및 톤업패드 사업도 확장.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>셀바이오휴먼텍, 2공장 이달 준공…11월 시운전ㆍ여드름패치 캐파 2배</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>코스나인과 바이오비쥬 주가가 상승세를 보이며 화장품 관련 종목에 대한 투자 관심이 확대.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>코스나인·바이오비쥬 주가 화색도네…화장품주 다시 불붙나</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026.09.11</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>기사발행일</t>
@@ -730,7 +692,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -821,19 +783,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="15" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -842,6 +791,9 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -879,6 +831,12 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -909,9 +867,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -949,7 +907,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1055,7 +1013,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1197,7 +1155,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1206,26 +1164,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9568EB5E-3B33-4B24-8B2F-C7967274DF5F}">
   <dimension ref="A1:D29"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.03515625" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="26.625" customWidth="1"/>
-    <col min="5" max="16384" width="9" style="1"/>
+    <col min="1" max="4" width="26.61328125" customWidth="1"/>
+    <col min="5" max="16384" width="9.03515625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" customFormat="1" ht="80.099999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="38" t="s">
+    <row r="1" spans="1:4" customFormat="1" ht="80.099999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="40"/>
-    </row>
-    <row r="2" spans="1:4" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="37"/>
+    </row>
+    <row r="2" spans="1:4" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>4</v>
@@ -1234,7 +1192,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:4" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
         <v>5</v>
       </c>
@@ -1245,186 +1203,198 @@
         <v>8</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="41"/>
-      <c r="B4" s="42"/>
-      <c r="C4" s="42"/>
-      <c r="D4" s="43"/>
-    </row>
-    <row r="5" spans="1:4" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="30"/>
-      <c r="D5" s="31"/>
-    </row>
-    <row r="6" spans="1:4" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="27"/>
-      <c r="B6" s="32"/>
-      <c r="C6" s="33"/>
-      <c r="D6" s="34"/>
-    </row>
-    <row r="7" spans="1:4" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="27"/>
-      <c r="B7" s="32"/>
-      <c r="C7" s="33"/>
-      <c r="D7" s="34"/>
-    </row>
-    <row r="8" spans="1:4" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27"/>
-      <c r="B8" s="32"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="34"/>
-    </row>
-    <row r="9" spans="1:4" customFormat="1" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="28"/>
-      <c r="B9" s="35"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="37"/>
-    </row>
-    <row r="10" spans="1:4" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="29"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="31"/>
-    </row>
-    <row r="11" spans="1:4" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="27"/>
-      <c r="B11" s="32"/>
-      <c r="C11" s="33"/>
-      <c r="D11" s="34"/>
-    </row>
-    <row r="12" spans="1:4" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="27"/>
-      <c r="B12" s="32"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="34"/>
-    </row>
-    <row r="13" spans="1:4" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="27"/>
-      <c r="B13" s="32"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="34"/>
-    </row>
-    <row r="14" spans="1:4" customFormat="1" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="27"/>
-      <c r="B14" s="35"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="37"/>
-    </row>
-    <row r="15" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="29"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="31"/>
-    </row>
-    <row r="16" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="27"/>
-      <c r="B16" s="32"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="34"/>
-    </row>
-    <row r="17" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="27"/>
-      <c r="B17" s="32"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="34"/>
-    </row>
-    <row r="18" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="27"/>
-      <c r="B18" s="32"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="34"/>
-    </row>
-    <row r="19" spans="1:4" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="28"/>
-      <c r="B19" s="35"/>
-      <c r="C19" s="36"/>
-      <c r="D19" s="37"/>
-    </row>
-    <row r="20" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" s="29"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="31"/>
-    </row>
-    <row r="21" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="27"/>
-      <c r="B21" s="32"/>
-      <c r="C21" s="33"/>
-      <c r="D21" s="34"/>
-    </row>
-    <row r="22" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="27"/>
-      <c r="B22" s="32"/>
-      <c r="C22" s="33"/>
-      <c r="D22" s="34"/>
-    </row>
-    <row r="23" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="27"/>
-      <c r="B23" s="32"/>
-      <c r="C23" s="33"/>
-      <c r="D23" s="34"/>
-    </row>
-    <row r="24" spans="1:4" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="28"/>
-      <c r="B24" s="35"/>
-      <c r="C24" s="36"/>
-      <c r="D24" s="37"/>
-    </row>
-    <row r="25" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="B25" s="29"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="31"/>
-    </row>
-    <row r="26" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="27"/>
-      <c r="B26" s="32"/>
-      <c r="C26" s="33"/>
-      <c r="D26" s="34"/>
-    </row>
-    <row r="27" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="27"/>
-      <c r="B27" s="32"/>
-      <c r="C27" s="33"/>
-      <c r="D27" s="34"/>
-    </row>
-    <row r="28" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="27"/>
-      <c r="B28" s="32"/>
-      <c r="C28" s="33"/>
-      <c r="D28" s="34"/>
-    </row>
-    <row r="29" spans="1:4" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="28"/>
-      <c r="B29" s="35"/>
-      <c r="C29" s="36"/>
-      <c r="D29" s="37"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="38"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="40"/>
+    </row>
+    <row r="5" spans="1:4" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="26"/>
+      <c r="D5" s="27"/>
+    </row>
+    <row r="6" spans="1:4" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="28"/>
+      <c r="B6" s="29"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="31"/>
+    </row>
+    <row r="7" spans="1:4" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="28"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="31"/>
+    </row>
+    <row r="8" spans="1:4" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="28"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="31"/>
+    </row>
+    <row r="9" spans="1:4" customFormat="1" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="42"/>
+      <c r="B9" s="32"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="34"/>
+    </row>
+    <row r="10" spans="1:4" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="25"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="27"/>
+    </row>
+    <row r="11" spans="1:4" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="28"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="31"/>
+    </row>
+    <row r="12" spans="1:4" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="28"/>
+      <c r="B12" s="29"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="31"/>
+    </row>
+    <row r="13" spans="1:4" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="28"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="31"/>
+    </row>
+    <row r="14" spans="1:4" customFormat="1" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="28"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="34"/>
+    </row>
+    <row r="15" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="41" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="25"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="27"/>
+    </row>
+    <row r="16" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="28"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="31"/>
+    </row>
+    <row r="17" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="28"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="31"/>
+    </row>
+    <row r="18" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="28"/>
+      <c r="B18" s="29"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="31"/>
+    </row>
+    <row r="19" spans="1:4" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="42"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="33"/>
+      <c r="D19" s="34"/>
+    </row>
+    <row r="20" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="25"/>
+      <c r="C20" s="26"/>
+      <c r="D20" s="27"/>
+    </row>
+    <row r="21" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="28"/>
+      <c r="B21" s="29"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="31"/>
+    </row>
+    <row r="22" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="28"/>
+      <c r="B22" s="29"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="31"/>
+    </row>
+    <row r="23" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="28"/>
+      <c r="B23" s="29"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="31"/>
+    </row>
+    <row r="24" spans="1:4" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="42"/>
+      <c r="B24" s="32"/>
+      <c r="C24" s="33"/>
+      <c r="D24" s="34"/>
+    </row>
+    <row r="25" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="41" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" s="25"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="27"/>
+    </row>
+    <row r="26" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="28"/>
+      <c r="B26" s="29"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="31"/>
+    </row>
+    <row r="27" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="28"/>
+      <c r="B27" s="29"/>
+      <c r="C27" s="30"/>
+      <c r="D27" s="31"/>
+    </row>
+    <row r="28" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="28"/>
+      <c r="B28" s="29"/>
+      <c r="C28" s="30"/>
+      <c r="D28" s="31"/>
+    </row>
+    <row r="29" spans="1:4" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="42"/>
+      <c r="B29" s="32"/>
+      <c r="C29" s="33"/>
+      <c r="D29" s="34"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="32">
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="A10:A14"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="A25:A29"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="A20:A24"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A15:A19"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="B6:D6"/>
@@ -1433,24 +1403,12 @@
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="B8:D8"/>
-    <mergeCell ref="A15:A19"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A20:A24"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="A25:A29"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="A10:A14"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B14:D14"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1459,30 +1417,30 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDD71AC8-49AB-4AA8-84FC-BB7060B2DF6F}">
-  <dimension ref="A1:I113"/>
-  <sheetFormatPr defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I111"/>
+  <sheetFormatPr defaultColWidth="9.03515625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.125" style="5" customWidth="1"/>
-    <col min="2" max="4" width="13.75" style="5" customWidth="1"/>
-    <col min="5" max="5" width="75.625" style="23" customWidth="1"/>
-    <col min="6" max="6" width="75.625" style="11" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="10.1484375" style="5" customWidth="1"/>
+    <col min="2" max="4" width="13.73828125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="75.6328125" style="23" customWidth="1"/>
+    <col min="6" max="6" width="75.6328125" style="11" customWidth="1"/>
+    <col min="7" max="16384" width="9.03515625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="44" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
+    <row r="1" spans="1:9" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
       <c r="G1" s="19"/>
       <c r="H1" s="19"/>
       <c r="I1" s="19"/>
     </row>
-    <row r="2" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1490,7 +1448,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D2" s="18" t="s">
         <v>9</v>
@@ -1502,49 +1460,29 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="25" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="25" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
+        <v>1</v>
+      </c>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="7"/>
+    </row>
+    <row r="4" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="8"/>
+    </row>
+    <row r="5" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -1552,9 +1490,9 @@
       <c r="E5" s="21"/>
       <c r="F5" s="7"/>
     </row>
-    <row r="6" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -1562,9 +1500,9 @@
       <c r="E6" s="21"/>
       <c r="F6" s="8"/>
     </row>
-    <row r="7" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
@@ -1572,9 +1510,9 @@
       <c r="E7" s="21"/>
       <c r="F7" s="7"/>
     </row>
-    <row r="8" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -1582,19 +1520,19 @@
       <c r="E8" s="21"/>
       <c r="F8" s="8"/>
     </row>
-    <row r="9" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
-      <c r="E9" s="21"/>
+      <c r="E9" s="24"/>
       <c r="F9" s="7"/>
     </row>
-    <row r="10" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -1602,19 +1540,19 @@
       <c r="E10" s="21"/>
       <c r="F10" s="8"/>
     </row>
-    <row r="11" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
-      <c r="E11" s="24"/>
+      <c r="E11" s="21"/>
       <c r="F11" s="7"/>
     </row>
-    <row r="12" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -1622,9 +1560,9 @@
       <c r="E12" s="21"/>
       <c r="F12" s="8"/>
     </row>
-    <row r="13" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -1632,9 +1570,9 @@
       <c r="E13" s="21"/>
       <c r="F13" s="7"/>
     </row>
-    <row r="14" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -1642,9 +1580,9 @@
       <c r="E14" s="21"/>
       <c r="F14" s="8"/>
     </row>
-    <row r="15" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
@@ -1652,9 +1590,9 @@
       <c r="E15" s="21"/>
       <c r="F15" s="7"/>
     </row>
-    <row r="16" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -1662,9 +1600,9 @@
       <c r="E16" s="21"/>
       <c r="F16" s="8"/>
     </row>
-    <row r="17" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -1672,9 +1610,9 @@
       <c r="E17" s="21"/>
       <c r="F17" s="7"/>
     </row>
-    <row r="18" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -1682,9 +1620,9 @@
       <c r="E18" s="21"/>
       <c r="F18" s="8"/>
     </row>
-    <row r="19" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
@@ -1692,9 +1630,9 @@
       <c r="E19" s="21"/>
       <c r="F19" s="7"/>
     </row>
-    <row r="20" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -1702,29 +1640,29 @@
       <c r="E20" s="21"/>
       <c r="F20" s="8"/>
     </row>
-    <row r="21" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="21"/>
-      <c r="F21" s="7"/>
-    </row>
-    <row r="22" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F21" s="8"/>
+    </row>
+    <row r="22" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="21"/>
-      <c r="F22" s="8"/>
-    </row>
-    <row r="23" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F22" s="7"/>
+    </row>
+    <row r="23" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
@@ -1732,29 +1670,29 @@
       <c r="E23" s="21"/>
       <c r="F23" s="8"/>
     </row>
-    <row r="24" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="21"/>
-      <c r="F24" s="7"/>
-    </row>
-    <row r="25" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F24" s="8"/>
+    </row>
+    <row r="25" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="21"/>
-      <c r="F25" s="8"/>
-    </row>
-    <row r="26" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F25" s="7"/>
+    </row>
+    <row r="26" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
@@ -1762,29 +1700,29 @@
       <c r="E26" s="21"/>
       <c r="F26" s="8"/>
     </row>
-    <row r="27" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B27" s="9"/>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="21"/>
-      <c r="F27" s="7"/>
-    </row>
-    <row r="28" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F27" s="8"/>
+    </row>
+    <row r="28" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="21"/>
-      <c r="F28" s="8"/>
-    </row>
-    <row r="29" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F28" s="7"/>
+    </row>
+    <row r="29" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
@@ -1792,29 +1730,29 @@
       <c r="E29" s="21"/>
       <c r="F29" s="8"/>
     </row>
-    <row r="30" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="21"/>
-      <c r="F30" s="7"/>
-    </row>
-    <row r="31" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F30" s="8"/>
+    </row>
+    <row r="31" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="21"/>
-      <c r="F31" s="8"/>
-    </row>
-    <row r="32" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F31" s="7"/>
+    </row>
+    <row r="32" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
@@ -1822,29 +1760,29 @@
       <c r="E32" s="21"/>
       <c r="F32" s="8"/>
     </row>
-    <row r="33" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
       <c r="E33" s="21"/>
-      <c r="F33" s="7"/>
-    </row>
-    <row r="34" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F33" s="8"/>
+    </row>
+    <row r="34" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="21"/>
-      <c r="F34" s="8"/>
-    </row>
-    <row r="35" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F34" s="7"/>
+    </row>
+    <row r="35" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
@@ -1852,29 +1790,29 @@
       <c r="E35" s="21"/>
       <c r="F35" s="8"/>
     </row>
-    <row r="36" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
       <c r="E36" s="21"/>
-      <c r="F36" s="7"/>
-    </row>
-    <row r="37" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F36" s="8"/>
+    </row>
+    <row r="37" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
       <c r="E37" s="21"/>
-      <c r="F37" s="8"/>
-    </row>
-    <row r="38" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F37" s="7"/>
+    </row>
+    <row r="38" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
@@ -1882,29 +1820,29 @@
       <c r="E38" s="21"/>
       <c r="F38" s="8"/>
     </row>
-    <row r="39" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
       <c r="E39" s="21"/>
-      <c r="F39" s="7"/>
-    </row>
-    <row r="40" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F39" s="8"/>
+    </row>
+    <row r="40" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
       <c r="E40" s="21"/>
-      <c r="F40" s="8"/>
-    </row>
-    <row r="41" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F40" s="7"/>
+    </row>
+    <row r="41" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B41" s="9"/>
       <c r="C41" s="9"/>
@@ -1912,9 +1850,9 @@
       <c r="E41" s="21"/>
       <c r="F41" s="8"/>
     </row>
-    <row r="42" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B42" s="9"/>
       <c r="C42" s="9"/>
@@ -1922,9 +1860,9 @@
       <c r="E42" s="21"/>
       <c r="F42" s="7"/>
     </row>
-    <row r="43" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
@@ -1932,29 +1870,29 @@
       <c r="E43" s="21"/>
       <c r="F43" s="8"/>
     </row>
-    <row r="44" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B44" s="9"/>
       <c r="C44" s="9"/>
       <c r="D44" s="9"/>
       <c r="E44" s="21"/>
-      <c r="F44" s="7"/>
-    </row>
-    <row r="45" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F44" s="8"/>
+    </row>
+    <row r="45" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B45" s="9"/>
       <c r="C45" s="9"/>
       <c r="D45" s="9"/>
       <c r="E45" s="21"/>
-      <c r="F45" s="8"/>
-    </row>
-    <row r="46" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F45" s="7"/>
+    </row>
+    <row r="46" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
@@ -1962,29 +1900,29 @@
       <c r="E46" s="21"/>
       <c r="F46" s="8"/>
     </row>
-    <row r="47" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B47" s="9"/>
       <c r="C47" s="9"/>
       <c r="D47" s="9"/>
       <c r="E47" s="21"/>
-      <c r="F47" s="7"/>
-    </row>
-    <row r="48" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F47" s="8"/>
+    </row>
+    <row r="48" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B48" s="9"/>
       <c r="C48" s="9"/>
       <c r="D48" s="9"/>
       <c r="E48" s="21"/>
-      <c r="F48" s="8"/>
-    </row>
-    <row r="49" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F48" s="7"/>
+    </row>
+    <row r="49" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B49" s="9"/>
       <c r="C49" s="9"/>
@@ -1992,9 +1930,9 @@
       <c r="E49" s="21"/>
       <c r="F49" s="8"/>
     </row>
-    <row r="50" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B50" s="9"/>
       <c r="C50" s="9"/>
@@ -2002,9 +1940,9 @@
       <c r="E50" s="21"/>
       <c r="F50" s="7"/>
     </row>
-    <row r="51" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B51" s="9"/>
       <c r="C51" s="9"/>
@@ -2012,9 +1950,9 @@
       <c r="E51" s="21"/>
       <c r="F51" s="8"/>
     </row>
-    <row r="52" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B52" s="9"/>
       <c r="C52" s="9"/>
@@ -2022,438 +1960,418 @@
       <c r="E52" s="21"/>
       <c r="F52" s="7"/>
     </row>
-    <row r="53" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="4">
-        <v>49</v>
-      </c>
-      <c r="B53" s="9"/>
-      <c r="C53" s="9"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="21"/>
-      <c r="F53" s="8"/>
-    </row>
-    <row r="54" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="4">
-        <v>50</v>
-      </c>
-      <c r="B54" s="9"/>
-      <c r="C54" s="9"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="21"/>
-      <c r="F54" s="7"/>
-    </row>
-    <row r="55" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="10"/>
+      <c r="C53" s="10"/>
+      <c r="D53" s="10"/>
+      <c r="E53" s="22"/>
+      <c r="F53" s="6"/>
+    </row>
+    <row r="54" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="10"/>
+      <c r="C54" s="10"/>
+      <c r="D54" s="10"/>
+      <c r="E54" s="22"/>
+      <c r="F54" s="6"/>
+    </row>
+    <row r="55" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="10"/>
       <c r="C55" s="10"/>
       <c r="D55" s="10"/>
       <c r="E55" s="22"/>
       <c r="F55" s="6"/>
     </row>
-    <row r="56" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="10"/>
       <c r="C56" s="10"/>
       <c r="D56" s="10"/>
       <c r="E56" s="22"/>
       <c r="F56" s="6"/>
     </row>
-    <row r="57" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="10"/>
       <c r="C57" s="10"/>
       <c r="D57" s="10"/>
       <c r="E57" s="22"/>
       <c r="F57" s="6"/>
     </row>
-    <row r="58" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="10"/>
       <c r="C58" s="10"/>
       <c r="D58" s="10"/>
       <c r="E58" s="22"/>
       <c r="F58" s="6"/>
     </row>
-    <row r="59" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="10"/>
       <c r="C59" s="10"/>
       <c r="D59" s="10"/>
       <c r="E59" s="22"/>
       <c r="F59" s="6"/>
     </row>
-    <row r="60" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="10"/>
       <c r="C60" s="10"/>
       <c r="D60" s="10"/>
       <c r="E60" s="22"/>
       <c r="F60" s="6"/>
     </row>
-    <row r="61" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="10"/>
       <c r="C61" s="10"/>
       <c r="D61" s="10"/>
       <c r="E61" s="22"/>
       <c r="F61" s="6"/>
     </row>
-    <row r="62" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="10"/>
       <c r="C62" s="10"/>
       <c r="D62" s="10"/>
       <c r="E62" s="22"/>
       <c r="F62" s="6"/>
     </row>
-    <row r="63" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="10"/>
       <c r="C63" s="10"/>
       <c r="D63" s="10"/>
       <c r="E63" s="22"/>
       <c r="F63" s="6"/>
     </row>
-    <row r="64" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B64" s="10"/>
       <c r="C64" s="10"/>
       <c r="D64" s="10"/>
       <c r="E64" s="22"/>
       <c r="F64" s="6"/>
     </row>
-    <row r="65" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="10"/>
       <c r="C65" s="10"/>
       <c r="D65" s="10"/>
       <c r="E65" s="22"/>
       <c r="F65" s="6"/>
     </row>
-    <row r="66" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="10"/>
       <c r="C66" s="10"/>
       <c r="D66" s="10"/>
       <c r="E66" s="22"/>
       <c r="F66" s="6"/>
     </row>
-    <row r="67" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="10"/>
       <c r="C67" s="10"/>
       <c r="D67" s="10"/>
       <c r="E67" s="22"/>
       <c r="F67" s="6"/>
     </row>
-    <row r="68" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="10"/>
       <c r="C68" s="10"/>
       <c r="D68" s="10"/>
       <c r="E68" s="22"/>
       <c r="F68" s="6"/>
     </row>
-    <row r="69" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B69" s="10"/>
       <c r="C69" s="10"/>
       <c r="D69" s="10"/>
       <c r="E69" s="22"/>
       <c r="F69" s="6"/>
     </row>
-    <row r="70" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="10"/>
       <c r="C70" s="10"/>
       <c r="D70" s="10"/>
       <c r="E70" s="22"/>
       <c r="F70" s="6"/>
     </row>
-    <row r="71" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="10"/>
       <c r="C71" s="10"/>
       <c r="D71" s="10"/>
       <c r="E71" s="22"/>
       <c r="F71" s="6"/>
     </row>
-    <row r="72" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B72" s="10"/>
       <c r="C72" s="10"/>
       <c r="D72" s="10"/>
       <c r="E72" s="22"/>
       <c r="F72" s="6"/>
     </row>
-    <row r="73" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B73" s="10"/>
       <c r="C73" s="10"/>
       <c r="D73" s="10"/>
       <c r="E73" s="22"/>
       <c r="F73" s="6"/>
     </row>
-    <row r="74" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" s="10"/>
       <c r="C74" s="10"/>
       <c r="D74" s="10"/>
       <c r="E74" s="22"/>
       <c r="F74" s="6"/>
     </row>
-    <row r="75" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B75" s="10"/>
       <c r="C75" s="10"/>
       <c r="D75" s="10"/>
       <c r="E75" s="22"/>
       <c r="F75" s="6"/>
     </row>
-    <row r="76" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B76" s="10"/>
       <c r="C76" s="10"/>
       <c r="D76" s="10"/>
       <c r="E76" s="22"/>
       <c r="F76" s="6"/>
     </row>
-    <row r="77" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="10"/>
       <c r="C77" s="10"/>
       <c r="D77" s="10"/>
       <c r="E77" s="22"/>
       <c r="F77" s="6"/>
     </row>
-    <row r="78" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B78" s="10"/>
       <c r="C78" s="10"/>
       <c r="D78" s="10"/>
       <c r="E78" s="22"/>
       <c r="F78" s="6"/>
     </row>
-    <row r="79" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B79" s="10"/>
       <c r="C79" s="10"/>
       <c r="D79" s="10"/>
       <c r="E79" s="22"/>
       <c r="F79" s="6"/>
     </row>
-    <row r="80" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B80" s="10"/>
       <c r="C80" s="10"/>
       <c r="D80" s="10"/>
       <c r="E80" s="22"/>
       <c r="F80" s="6"/>
     </row>
-    <row r="81" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B81" s="10"/>
       <c r="C81" s="10"/>
       <c r="D81" s="10"/>
       <c r="E81" s="22"/>
       <c r="F81" s="6"/>
     </row>
-    <row r="82" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" s="10"/>
       <c r="C82" s="10"/>
       <c r="D82" s="10"/>
       <c r="E82" s="22"/>
       <c r="F82" s="6"/>
     </row>
-    <row r="83" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B83" s="10"/>
       <c r="C83" s="10"/>
       <c r="D83" s="10"/>
       <c r="E83" s="22"/>
       <c r="F83" s="6"/>
     </row>
-    <row r="84" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B84" s="10"/>
       <c r="C84" s="10"/>
       <c r="D84" s="10"/>
       <c r="E84" s="22"/>
       <c r="F84" s="6"/>
     </row>
-    <row r="85" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B85" s="10"/>
       <c r="C85" s="10"/>
       <c r="D85" s="10"/>
       <c r="E85" s="22"/>
       <c r="F85" s="6"/>
     </row>
-    <row r="86" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B86" s="10"/>
       <c r="C86" s="10"/>
       <c r="D86" s="10"/>
       <c r="E86" s="22"/>
       <c r="F86" s="6"/>
     </row>
-    <row r="87" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B87" s="10"/>
       <c r="C87" s="10"/>
       <c r="D87" s="10"/>
       <c r="E87" s="22"/>
       <c r="F87" s="6"/>
     </row>
-    <row r="88" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B88" s="10"/>
       <c r="C88" s="10"/>
       <c r="D88" s="10"/>
       <c r="E88" s="22"/>
       <c r="F88" s="6"/>
     </row>
-    <row r="89" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B89" s="10"/>
       <c r="C89" s="10"/>
       <c r="D89" s="10"/>
       <c r="E89" s="22"/>
       <c r="F89" s="6"/>
     </row>
-    <row r="90" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B90" s="10"/>
       <c r="C90" s="10"/>
       <c r="D90" s="10"/>
       <c r="E90" s="22"/>
       <c r="F90" s="6"/>
     </row>
-    <row r="91" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B91" s="10"/>
       <c r="C91" s="10"/>
       <c r="D91" s="10"/>
       <c r="E91" s="22"/>
       <c r="F91" s="6"/>
     </row>
-    <row r="92" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B92" s="10"/>
       <c r="C92" s="10"/>
       <c r="D92" s="10"/>
       <c r="E92" s="22"/>
       <c r="F92" s="6"/>
     </row>
-    <row r="93" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B93" s="10"/>
       <c r="C93" s="10"/>
       <c r="D93" s="10"/>
       <c r="E93" s="22"/>
       <c r="F93" s="6"/>
     </row>
-    <row r="94" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B94" s="10"/>
       <c r="C94" s="10"/>
       <c r="D94" s="10"/>
       <c r="E94" s="22"/>
       <c r="F94" s="6"/>
     </row>
-    <row r="95" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B95" s="10"/>
       <c r="C95" s="10"/>
       <c r="D95" s="10"/>
       <c r="E95" s="22"/>
       <c r="F95" s="6"/>
     </row>
-    <row r="96" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B96" s="10"/>
       <c r="C96" s="10"/>
       <c r="D96" s="10"/>
       <c r="E96" s="22"/>
       <c r="F96" s="6"/>
     </row>
-    <row r="97" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B97" s="10"/>
       <c r="C97" s="10"/>
       <c r="D97" s="10"/>
       <c r="E97" s="22"/>
       <c r="F97" s="6"/>
     </row>
-    <row r="98" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B98" s="10"/>
       <c r="C98" s="10"/>
       <c r="D98" s="10"/>
       <c r="E98" s="22"/>
       <c r="F98" s="6"/>
     </row>
-    <row r="99" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B99" s="10"/>
       <c r="C99" s="10"/>
       <c r="D99" s="10"/>
       <c r="E99" s="22"/>
       <c r="F99" s="6"/>
     </row>
-    <row r="100" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B100" s="10"/>
       <c r="C100" s="10"/>
       <c r="D100" s="10"/>
       <c r="E100" s="22"/>
       <c r="F100" s="6"/>
     </row>
-    <row r="101" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B101" s="10"/>
       <c r="C101" s="10"/>
       <c r="D101" s="10"/>
       <c r="E101" s="22"/>
       <c r="F101" s="6"/>
     </row>
-    <row r="102" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B102" s="10"/>
       <c r="C102" s="10"/>
       <c r="D102" s="10"/>
       <c r="E102" s="22"/>
       <c r="F102" s="6"/>
     </row>
-    <row r="103" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B103" s="10"/>
       <c r="C103" s="10"/>
       <c r="D103" s="10"/>
       <c r="E103" s="22"/>
       <c r="F103" s="6"/>
     </row>
-    <row r="104" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B104" s="10"/>
       <c r="C104" s="10"/>
       <c r="D104" s="10"/>
       <c r="E104" s="22"/>
       <c r="F104" s="6"/>
     </row>
-    <row r="105" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B105" s="10"/>
       <c r="C105" s="10"/>
       <c r="D105" s="10"/>
       <c r="E105" s="22"/>
       <c r="F105" s="6"/>
     </row>
-    <row r="106" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B106" s="10"/>
       <c r="C106" s="10"/>
       <c r="D106" s="10"/>
       <c r="E106" s="22"/>
       <c r="F106" s="6"/>
     </row>
-    <row r="107" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B107" s="10"/>
       <c r="C107" s="10"/>
       <c r="D107" s="10"/>
       <c r="E107" s="22"/>
       <c r="F107" s="6"/>
     </row>
-    <row r="108" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B108" s="10"/>
       <c r="C108" s="10"/>
       <c r="D108" s="10"/>
       <c r="E108" s="22"/>
       <c r="F108" s="6"/>
     </row>
-    <row r="109" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B109" s="10"/>
       <c r="C109" s="10"/>
       <c r="D109" s="10"/>
       <c r="E109" s="22"/>
       <c r="F109" s="6"/>
     </row>
-    <row r="110" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B110" s="10"/>
       <c r="C110" s="10"/>
       <c r="D110" s="10"/>
       <c r="E110" s="22"/>
       <c r="F110" s="6"/>
     </row>
-    <row r="111" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B111" s="10"/>
       <c r="C111" s="10"/>
       <c r="D111" s="10"/>
       <c r="E111" s="22"/>
       <c r="F111" s="6"/>
-    </row>
-    <row r="112" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B112" s="10"/>
-      <c r="C112" s="10"/>
-      <c r="D112" s="10"/>
-      <c r="E112" s="22"/>
-      <c r="F112" s="6"/>
-    </row>
-    <row r="113" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B113" s="10"/>
-      <c r="C113" s="10"/>
-      <c r="D113" s="10"/>
-      <c r="E113" s="22"/>
-      <c r="F113" s="6"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
@@ -2461,10 +2379,6 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="F3" r:id="rId1" xr:uid="{A37655CA-487B-4589-8462-D68F90DDD3DF}"/>
-    <hyperlink ref="F4" r:id="rId2" xr:uid="{B50FC2E0-BDB2-43B4-A0B4-7CF704D8AF25}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2472,29 +2386,29 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72CDF01A-0F82-4C02-886F-A8C330A12F7E}">
   <dimension ref="A1:I111"/>
-  <sheetFormatPr defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.03515625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.125" style="5" customWidth="1"/>
-    <col min="2" max="4" width="13.75" style="5" customWidth="1"/>
-    <col min="5" max="5" width="75.625" style="23" customWidth="1"/>
-    <col min="6" max="6" width="75.625" style="11" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="10.1484375" style="5" customWidth="1"/>
+    <col min="2" max="4" width="13.73828125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="75.6328125" style="23" customWidth="1"/>
+    <col min="6" max="6" width="75.6328125" style="11" customWidth="1"/>
+    <col min="7" max="16384" width="9.03515625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
+    <row r="1" spans="1:9" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
       <c r="G1" s="19"/>
       <c r="H1" s="19"/>
       <c r="I1" s="19"/>
     </row>
-    <row r="2" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -2502,7 +2416,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D2" s="18" t="s">
         <v>9</v>
@@ -2514,7 +2428,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>1</v>
       </c>
@@ -2524,7 +2438,7 @@
       <c r="E3" s="21"/>
       <c r="F3" s="7"/>
     </row>
-    <row r="4" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>2</v>
       </c>
@@ -2534,7 +2448,7 @@
       <c r="E4" s="21"/>
       <c r="F4" s="8"/>
     </row>
-    <row r="5" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>3</v>
       </c>
@@ -2544,7 +2458,7 @@
       <c r="E5" s="21"/>
       <c r="F5" s="7"/>
     </row>
-    <row r="6" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>4</v>
       </c>
@@ -2554,7 +2468,7 @@
       <c r="E6" s="21"/>
       <c r="F6" s="8"/>
     </row>
-    <row r="7" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>5</v>
       </c>
@@ -2564,7 +2478,7 @@
       <c r="E7" s="21"/>
       <c r="F7" s="7"/>
     </row>
-    <row r="8" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>6</v>
       </c>
@@ -2574,7 +2488,7 @@
       <c r="E8" s="21"/>
       <c r="F8" s="8"/>
     </row>
-    <row r="9" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>7</v>
       </c>
@@ -2584,7 +2498,7 @@
       <c r="E9" s="24"/>
       <c r="F9" s="7"/>
     </row>
-    <row r="10" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>8</v>
       </c>
@@ -2594,7 +2508,7 @@
       <c r="E10" s="21"/>
       <c r="F10" s="8"/>
     </row>
-    <row r="11" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>9</v>
       </c>
@@ -2604,7 +2518,7 @@
       <c r="E11" s="21"/>
       <c r="F11" s="7"/>
     </row>
-    <row r="12" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>10</v>
       </c>
@@ -2614,7 +2528,7 @@
       <c r="E12" s="21"/>
       <c r="F12" s="8"/>
     </row>
-    <row r="13" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>11</v>
       </c>
@@ -2624,7 +2538,7 @@
       <c r="E13" s="21"/>
       <c r="F13" s="7"/>
     </row>
-    <row r="14" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>12</v>
       </c>
@@ -2634,7 +2548,7 @@
       <c r="E14" s="21"/>
       <c r="F14" s="8"/>
     </row>
-    <row r="15" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>13</v>
       </c>
@@ -2644,7 +2558,7 @@
       <c r="E15" s="21"/>
       <c r="F15" s="7"/>
     </row>
-    <row r="16" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>14</v>
       </c>
@@ -2654,7 +2568,7 @@
       <c r="E16" s="21"/>
       <c r="F16" s="8"/>
     </row>
-    <row r="17" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>15</v>
       </c>
@@ -2664,7 +2578,7 @@
       <c r="E17" s="21"/>
       <c r="F17" s="7"/>
     </row>
-    <row r="18" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>16</v>
       </c>
@@ -2674,7 +2588,7 @@
       <c r="E18" s="21"/>
       <c r="F18" s="8"/>
     </row>
-    <row r="19" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>17</v>
       </c>
@@ -2684,7 +2598,7 @@
       <c r="E19" s="21"/>
       <c r="F19" s="7"/>
     </row>
-    <row r="20" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>18</v>
       </c>
@@ -2694,7 +2608,7 @@
       <c r="E20" s="21"/>
       <c r="F20" s="8"/>
     </row>
-    <row r="21" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>19</v>
       </c>
@@ -2704,7 +2618,7 @@
       <c r="E21" s="21"/>
       <c r="F21" s="8"/>
     </row>
-    <row r="22" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>20</v>
       </c>
@@ -2714,7 +2628,7 @@
       <c r="E22" s="21"/>
       <c r="F22" s="7"/>
     </row>
-    <row r="23" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>21</v>
       </c>
@@ -2724,7 +2638,7 @@
       <c r="E23" s="21"/>
       <c r="F23" s="8"/>
     </row>
-    <row r="24" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>22</v>
       </c>
@@ -2734,7 +2648,7 @@
       <c r="E24" s="21"/>
       <c r="F24" s="8"/>
     </row>
-    <row r="25" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>23</v>
       </c>
@@ -2744,7 +2658,7 @@
       <c r="E25" s="21"/>
       <c r="F25" s="7"/>
     </row>
-    <row r="26" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>24</v>
       </c>
@@ -2754,7 +2668,7 @@
       <c r="E26" s="21"/>
       <c r="F26" s="8"/>
     </row>
-    <row r="27" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>25</v>
       </c>
@@ -2764,7 +2678,7 @@
       <c r="E27" s="21"/>
       <c r="F27" s="8"/>
     </row>
-    <row r="28" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>26</v>
       </c>
@@ -2774,7 +2688,7 @@
       <c r="E28" s="21"/>
       <c r="F28" s="7"/>
     </row>
-    <row r="29" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>27</v>
       </c>
@@ -2784,7 +2698,7 @@
       <c r="E29" s="21"/>
       <c r="F29" s="8"/>
     </row>
-    <row r="30" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>28</v>
       </c>
@@ -2794,7 +2708,7 @@
       <c r="E30" s="21"/>
       <c r="F30" s="8"/>
     </row>
-    <row r="31" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>29</v>
       </c>
@@ -2804,7 +2718,7 @@
       <c r="E31" s="21"/>
       <c r="F31" s="7"/>
     </row>
-    <row r="32" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>30</v>
       </c>
@@ -2814,7 +2728,7 @@
       <c r="E32" s="21"/>
       <c r="F32" s="8"/>
     </row>
-    <row r="33" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>31</v>
       </c>
@@ -2824,7 +2738,7 @@
       <c r="E33" s="21"/>
       <c r="F33" s="8"/>
     </row>
-    <row r="34" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <v>32</v>
       </c>
@@ -2834,7 +2748,7 @@
       <c r="E34" s="21"/>
       <c r="F34" s="7"/>
     </row>
-    <row r="35" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>33</v>
       </c>
@@ -2844,7 +2758,7 @@
       <c r="E35" s="21"/>
       <c r="F35" s="8"/>
     </row>
-    <row r="36" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>34</v>
       </c>
@@ -2854,7 +2768,7 @@
       <c r="E36" s="21"/>
       <c r="F36" s="8"/>
     </row>
-    <row r="37" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>35</v>
       </c>
@@ -2864,7 +2778,7 @@
       <c r="E37" s="21"/>
       <c r="F37" s="7"/>
     </row>
-    <row r="38" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>36</v>
       </c>
@@ -2874,7 +2788,7 @@
       <c r="E38" s="21"/>
       <c r="F38" s="8"/>
     </row>
-    <row r="39" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>37</v>
       </c>
@@ -2884,7 +2798,7 @@
       <c r="E39" s="21"/>
       <c r="F39" s="8"/>
     </row>
-    <row r="40" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>38</v>
       </c>
@@ -2894,7 +2808,7 @@
       <c r="E40" s="21"/>
       <c r="F40" s="7"/>
     </row>
-    <row r="41" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>39</v>
       </c>
@@ -2904,7 +2818,7 @@
       <c r="E41" s="21"/>
       <c r="F41" s="8"/>
     </row>
-    <row r="42" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <v>40</v>
       </c>
@@ -2914,7 +2828,7 @@
       <c r="E42" s="21"/>
       <c r="F42" s="7"/>
     </row>
-    <row r="43" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>41</v>
       </c>
@@ -2924,7 +2838,7 @@
       <c r="E43" s="21"/>
       <c r="F43" s="8"/>
     </row>
-    <row r="44" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <v>42</v>
       </c>
@@ -2934,7 +2848,7 @@
       <c r="E44" s="21"/>
       <c r="F44" s="8"/>
     </row>
-    <row r="45" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>43</v>
       </c>
@@ -2944,7 +2858,7 @@
       <c r="E45" s="21"/>
       <c r="F45" s="7"/>
     </row>
-    <row r="46" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <v>44</v>
       </c>
@@ -2954,7 +2868,7 @@
       <c r="E46" s="21"/>
       <c r="F46" s="8"/>
     </row>
-    <row r="47" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <v>45</v>
       </c>
@@ -2964,7 +2878,7 @@
       <c r="E47" s="21"/>
       <c r="F47" s="8"/>
     </row>
-    <row r="48" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <v>46</v>
       </c>
@@ -2974,7 +2888,7 @@
       <c r="E48" s="21"/>
       <c r="F48" s="7"/>
     </row>
-    <row r="49" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>47</v>
       </c>
@@ -2984,7 +2898,7 @@
       <c r="E49" s="21"/>
       <c r="F49" s="8"/>
     </row>
-    <row r="50" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
         <v>48</v>
       </c>
@@ -2994,7 +2908,7 @@
       <c r="E50" s="21"/>
       <c r="F50" s="7"/>
     </row>
-    <row r="51" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <v>49</v>
       </c>
@@ -3004,7 +2918,7 @@
       <c r="E51" s="21"/>
       <c r="F51" s="8"/>
     </row>
-    <row r="52" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
         <v>50</v>
       </c>
@@ -3014,413 +2928,413 @@
       <c r="E52" s="21"/>
       <c r="F52" s="7"/>
     </row>
-    <row r="53" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="10"/>
       <c r="C53" s="10"/>
       <c r="D53" s="10"/>
       <c r="E53" s="22"/>
       <c r="F53" s="6"/>
     </row>
-    <row r="54" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="10"/>
       <c r="C54" s="10"/>
       <c r="D54" s="10"/>
       <c r="E54" s="22"/>
       <c r="F54" s="6"/>
     </row>
-    <row r="55" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="10"/>
       <c r="C55" s="10"/>
       <c r="D55" s="10"/>
       <c r="E55" s="22"/>
       <c r="F55" s="6"/>
     </row>
-    <row r="56" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="10"/>
       <c r="C56" s="10"/>
       <c r="D56" s="10"/>
       <c r="E56" s="22"/>
       <c r="F56" s="6"/>
     </row>
-    <row r="57" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="10"/>
       <c r="C57" s="10"/>
       <c r="D57" s="10"/>
       <c r="E57" s="22"/>
       <c r="F57" s="6"/>
     </row>
-    <row r="58" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="10"/>
       <c r="C58" s="10"/>
       <c r="D58" s="10"/>
       <c r="E58" s="22"/>
       <c r="F58" s="6"/>
     </row>
-    <row r="59" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="10"/>
       <c r="C59" s="10"/>
       <c r="D59" s="10"/>
       <c r="E59" s="22"/>
       <c r="F59" s="6"/>
     </row>
-    <row r="60" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="10"/>
       <c r="C60" s="10"/>
       <c r="D60" s="10"/>
       <c r="E60" s="22"/>
       <c r="F60" s="6"/>
     </row>
-    <row r="61" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="10"/>
       <c r="C61" s="10"/>
       <c r="D61" s="10"/>
       <c r="E61" s="22"/>
       <c r="F61" s="6"/>
     </row>
-    <row r="62" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="10"/>
       <c r="C62" s="10"/>
       <c r="D62" s="10"/>
       <c r="E62" s="22"/>
       <c r="F62" s="6"/>
     </row>
-    <row r="63" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="10"/>
       <c r="C63" s="10"/>
       <c r="D63" s="10"/>
       <c r="E63" s="22"/>
       <c r="F63" s="6"/>
     </row>
-    <row r="64" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B64" s="10"/>
       <c r="C64" s="10"/>
       <c r="D64" s="10"/>
       <c r="E64" s="22"/>
       <c r="F64" s="6"/>
     </row>
-    <row r="65" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="10"/>
       <c r="C65" s="10"/>
       <c r="D65" s="10"/>
       <c r="E65" s="22"/>
       <c r="F65" s="6"/>
     </row>
-    <row r="66" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="10"/>
       <c r="C66" s="10"/>
       <c r="D66" s="10"/>
       <c r="E66" s="22"/>
       <c r="F66" s="6"/>
     </row>
-    <row r="67" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="10"/>
       <c r="C67" s="10"/>
       <c r="D67" s="10"/>
       <c r="E67" s="22"/>
       <c r="F67" s="6"/>
     </row>
-    <row r="68" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="10"/>
       <c r="C68" s="10"/>
       <c r="D68" s="10"/>
       <c r="E68" s="22"/>
       <c r="F68" s="6"/>
     </row>
-    <row r="69" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B69" s="10"/>
       <c r="C69" s="10"/>
       <c r="D69" s="10"/>
       <c r="E69" s="22"/>
       <c r="F69" s="6"/>
     </row>
-    <row r="70" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="10"/>
       <c r="C70" s="10"/>
       <c r="D70" s="10"/>
       <c r="E70" s="22"/>
       <c r="F70" s="6"/>
     </row>
-    <row r="71" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="10"/>
       <c r="C71" s="10"/>
       <c r="D71" s="10"/>
       <c r="E71" s="22"/>
       <c r="F71" s="6"/>
     </row>
-    <row r="72" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B72" s="10"/>
       <c r="C72" s="10"/>
       <c r="D72" s="10"/>
       <c r="E72" s="22"/>
       <c r="F72" s="6"/>
     </row>
-    <row r="73" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B73" s="10"/>
       <c r="C73" s="10"/>
       <c r="D73" s="10"/>
       <c r="E73" s="22"/>
       <c r="F73" s="6"/>
     </row>
-    <row r="74" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" s="10"/>
       <c r="C74" s="10"/>
       <c r="D74" s="10"/>
       <c r="E74" s="22"/>
       <c r="F74" s="6"/>
     </row>
-    <row r="75" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B75" s="10"/>
       <c r="C75" s="10"/>
       <c r="D75" s="10"/>
       <c r="E75" s="22"/>
       <c r="F75" s="6"/>
     </row>
-    <row r="76" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B76" s="10"/>
       <c r="C76" s="10"/>
       <c r="D76" s="10"/>
       <c r="E76" s="22"/>
       <c r="F76" s="6"/>
     </row>
-    <row r="77" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="10"/>
       <c r="C77" s="10"/>
       <c r="D77" s="10"/>
       <c r="E77" s="22"/>
       <c r="F77" s="6"/>
     </row>
-    <row r="78" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B78" s="10"/>
       <c r="C78" s="10"/>
       <c r="D78" s="10"/>
       <c r="E78" s="22"/>
       <c r="F78" s="6"/>
     </row>
-    <row r="79" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B79" s="10"/>
       <c r="C79" s="10"/>
       <c r="D79" s="10"/>
       <c r="E79" s="22"/>
       <c r="F79" s="6"/>
     </row>
-    <row r="80" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B80" s="10"/>
       <c r="C80" s="10"/>
       <c r="D80" s="10"/>
       <c r="E80" s="22"/>
       <c r="F80" s="6"/>
     </row>
-    <row r="81" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B81" s="10"/>
       <c r="C81" s="10"/>
       <c r="D81" s="10"/>
       <c r="E81" s="22"/>
       <c r="F81" s="6"/>
     </row>
-    <row r="82" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" s="10"/>
       <c r="C82" s="10"/>
       <c r="D82" s="10"/>
       <c r="E82" s="22"/>
       <c r="F82" s="6"/>
     </row>
-    <row r="83" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B83" s="10"/>
       <c r="C83" s="10"/>
       <c r="D83" s="10"/>
       <c r="E83" s="22"/>
       <c r="F83" s="6"/>
     </row>
-    <row r="84" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B84" s="10"/>
       <c r="C84" s="10"/>
       <c r="D84" s="10"/>
       <c r="E84" s="22"/>
       <c r="F84" s="6"/>
     </row>
-    <row r="85" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B85" s="10"/>
       <c r="C85" s="10"/>
       <c r="D85" s="10"/>
       <c r="E85" s="22"/>
       <c r="F85" s="6"/>
     </row>
-    <row r="86" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B86" s="10"/>
       <c r="C86" s="10"/>
       <c r="D86" s="10"/>
       <c r="E86" s="22"/>
       <c r="F86" s="6"/>
     </row>
-    <row r="87" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B87" s="10"/>
       <c r="C87" s="10"/>
       <c r="D87" s="10"/>
       <c r="E87" s="22"/>
       <c r="F87" s="6"/>
     </row>
-    <row r="88" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B88" s="10"/>
       <c r="C88" s="10"/>
       <c r="D88" s="10"/>
       <c r="E88" s="22"/>
       <c r="F88" s="6"/>
     </row>
-    <row r="89" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B89" s="10"/>
       <c r="C89" s="10"/>
       <c r="D89" s="10"/>
       <c r="E89" s="22"/>
       <c r="F89" s="6"/>
     </row>
-    <row r="90" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B90" s="10"/>
       <c r="C90" s="10"/>
       <c r="D90" s="10"/>
       <c r="E90" s="22"/>
       <c r="F90" s="6"/>
     </row>
-    <row r="91" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B91" s="10"/>
       <c r="C91" s="10"/>
       <c r="D91" s="10"/>
       <c r="E91" s="22"/>
       <c r="F91" s="6"/>
     </row>
-    <row r="92" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B92" s="10"/>
       <c r="C92" s="10"/>
       <c r="D92" s="10"/>
       <c r="E92" s="22"/>
       <c r="F92" s="6"/>
     </row>
-    <row r="93" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B93" s="10"/>
       <c r="C93" s="10"/>
       <c r="D93" s="10"/>
       <c r="E93" s="22"/>
       <c r="F93" s="6"/>
     </row>
-    <row r="94" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B94" s="10"/>
       <c r="C94" s="10"/>
       <c r="D94" s="10"/>
       <c r="E94" s="22"/>
       <c r="F94" s="6"/>
     </row>
-    <row r="95" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B95" s="10"/>
       <c r="C95" s="10"/>
       <c r="D95" s="10"/>
       <c r="E95" s="22"/>
       <c r="F95" s="6"/>
     </row>
-    <row r="96" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B96" s="10"/>
       <c r="C96" s="10"/>
       <c r="D96" s="10"/>
       <c r="E96" s="22"/>
       <c r="F96" s="6"/>
     </row>
-    <row r="97" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B97" s="10"/>
       <c r="C97" s="10"/>
       <c r="D97" s="10"/>
       <c r="E97" s="22"/>
       <c r="F97" s="6"/>
     </row>
-    <row r="98" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B98" s="10"/>
       <c r="C98" s="10"/>
       <c r="D98" s="10"/>
       <c r="E98" s="22"/>
       <c r="F98" s="6"/>
     </row>
-    <row r="99" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B99" s="10"/>
       <c r="C99" s="10"/>
       <c r="D99" s="10"/>
       <c r="E99" s="22"/>
       <c r="F99" s="6"/>
     </row>
-    <row r="100" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B100" s="10"/>
       <c r="C100" s="10"/>
       <c r="D100" s="10"/>
       <c r="E100" s="22"/>
       <c r="F100" s="6"/>
     </row>
-    <row r="101" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B101" s="10"/>
       <c r="C101" s="10"/>
       <c r="D101" s="10"/>
       <c r="E101" s="22"/>
       <c r="F101" s="6"/>
     </row>
-    <row r="102" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B102" s="10"/>
       <c r="C102" s="10"/>
       <c r="D102" s="10"/>
       <c r="E102" s="22"/>
       <c r="F102" s="6"/>
     </row>
-    <row r="103" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B103" s="10"/>
       <c r="C103" s="10"/>
       <c r="D103" s="10"/>
       <c r="E103" s="22"/>
       <c r="F103" s="6"/>
     </row>
-    <row r="104" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B104" s="10"/>
       <c r="C104" s="10"/>
       <c r="D104" s="10"/>
       <c r="E104" s="22"/>
       <c r="F104" s="6"/>
     </row>
-    <row r="105" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B105" s="10"/>
       <c r="C105" s="10"/>
       <c r="D105" s="10"/>
       <c r="E105" s="22"/>
       <c r="F105" s="6"/>
     </row>
-    <row r="106" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B106" s="10"/>
       <c r="C106" s="10"/>
       <c r="D106" s="10"/>
       <c r="E106" s="22"/>
       <c r="F106" s="6"/>
     </row>
-    <row r="107" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B107" s="10"/>
       <c r="C107" s="10"/>
       <c r="D107" s="10"/>
       <c r="E107" s="22"/>
       <c r="F107" s="6"/>
     </row>
-    <row r="108" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B108" s="10"/>
       <c r="C108" s="10"/>
       <c r="D108" s="10"/>
       <c r="E108" s="22"/>
       <c r="F108" s="6"/>
     </row>
-    <row r="109" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B109" s="10"/>
       <c r="C109" s="10"/>
       <c r="D109" s="10"/>
       <c r="E109" s="22"/>
       <c r="F109" s="6"/>
     </row>
-    <row r="110" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B110" s="10"/>
       <c r="C110" s="10"/>
       <c r="D110" s="10"/>
       <c r="E110" s="22"/>
       <c r="F110" s="6"/>
     </row>
-    <row r="111" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B111" s="10"/>
       <c r="C111" s="10"/>
       <c r="D111" s="10"/>
@@ -3440,29 +3354,29 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B072DDC4-BB0F-42ED-BE28-2B364483FECE}">
   <dimension ref="A1:I111"/>
-  <sheetFormatPr defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.03515625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.125" style="5" customWidth="1"/>
-    <col min="2" max="4" width="13.75" style="5" customWidth="1"/>
-    <col min="5" max="5" width="75.625" style="23" customWidth="1"/>
-    <col min="6" max="6" width="75.625" style="11" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="10.1484375" style="5" customWidth="1"/>
+    <col min="2" max="4" width="13.73828125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="75.6328125" style="23" customWidth="1"/>
+    <col min="6" max="6" width="75.6328125" style="11" customWidth="1"/>
+    <col min="7" max="16384" width="9.03515625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="44" t="s">
-        <v>33</v>
-      </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
+    <row r="1" spans="1:9" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
       <c r="G1" s="19"/>
       <c r="H1" s="19"/>
       <c r="I1" s="19"/>
     </row>
-    <row r="2" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -3470,7 +3384,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D2" s="18" t="s">
         <v>9</v>
@@ -3482,7 +3396,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>1</v>
       </c>
@@ -3492,7 +3406,7 @@
       <c r="E3" s="21"/>
       <c r="F3" s="7"/>
     </row>
-    <row r="4" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>2</v>
       </c>
@@ -3502,7 +3416,7 @@
       <c r="E4" s="21"/>
       <c r="F4" s="8"/>
     </row>
-    <row r="5" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>3</v>
       </c>
@@ -3512,7 +3426,7 @@
       <c r="E5" s="21"/>
       <c r="F5" s="7"/>
     </row>
-    <row r="6" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>4</v>
       </c>
@@ -3522,7 +3436,7 @@
       <c r="E6" s="21"/>
       <c r="F6" s="8"/>
     </row>
-    <row r="7" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>5</v>
       </c>
@@ -3532,7 +3446,7 @@
       <c r="E7" s="21"/>
       <c r="F7" s="7"/>
     </row>
-    <row r="8" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>6</v>
       </c>
@@ -3542,7 +3456,7 @@
       <c r="E8" s="21"/>
       <c r="F8" s="8"/>
     </row>
-    <row r="9" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>7</v>
       </c>
@@ -3552,7 +3466,7 @@
       <c r="E9" s="24"/>
       <c r="F9" s="7"/>
     </row>
-    <row r="10" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>8</v>
       </c>
@@ -3562,7 +3476,7 @@
       <c r="E10" s="21"/>
       <c r="F10" s="8"/>
     </row>
-    <row r="11" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>9</v>
       </c>
@@ -3572,7 +3486,7 @@
       <c r="E11" s="21"/>
       <c r="F11" s="7"/>
     </row>
-    <row r="12" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>10</v>
       </c>
@@ -3582,7 +3496,7 @@
       <c r="E12" s="21"/>
       <c r="F12" s="8"/>
     </row>
-    <row r="13" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>11</v>
       </c>
@@ -3592,7 +3506,7 @@
       <c r="E13" s="21"/>
       <c r="F13" s="7"/>
     </row>
-    <row r="14" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>12</v>
       </c>
@@ -3602,7 +3516,7 @@
       <c r="E14" s="21"/>
       <c r="F14" s="8"/>
     </row>
-    <row r="15" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>13</v>
       </c>
@@ -3612,7 +3526,7 @@
       <c r="E15" s="21"/>
       <c r="F15" s="7"/>
     </row>
-    <row r="16" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>14</v>
       </c>
@@ -3622,7 +3536,7 @@
       <c r="E16" s="21"/>
       <c r="F16" s="8"/>
     </row>
-    <row r="17" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>15</v>
       </c>
@@ -3632,7 +3546,7 @@
       <c r="E17" s="21"/>
       <c r="F17" s="7"/>
     </row>
-    <row r="18" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>16</v>
       </c>
@@ -3642,7 +3556,7 @@
       <c r="E18" s="21"/>
       <c r="F18" s="8"/>
     </row>
-    <row r="19" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>17</v>
       </c>
@@ -3652,7 +3566,7 @@
       <c r="E19" s="21"/>
       <c r="F19" s="7"/>
     </row>
-    <row r="20" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>18</v>
       </c>
@@ -3662,7 +3576,7 @@
       <c r="E20" s="21"/>
       <c r="F20" s="8"/>
     </row>
-    <row r="21" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>19</v>
       </c>
@@ -3672,7 +3586,7 @@
       <c r="E21" s="21"/>
       <c r="F21" s="8"/>
     </row>
-    <row r="22" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>20</v>
       </c>
@@ -3682,7 +3596,7 @@
       <c r="E22" s="21"/>
       <c r="F22" s="7"/>
     </row>
-    <row r="23" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>21</v>
       </c>
@@ -3692,7 +3606,7 @@
       <c r="E23" s="21"/>
       <c r="F23" s="8"/>
     </row>
-    <row r="24" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>22</v>
       </c>
@@ -3702,7 +3616,7 @@
       <c r="E24" s="21"/>
       <c r="F24" s="8"/>
     </row>
-    <row r="25" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>23</v>
       </c>
@@ -3712,7 +3626,7 @@
       <c r="E25" s="21"/>
       <c r="F25" s="7"/>
     </row>
-    <row r="26" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>24</v>
       </c>
@@ -3722,7 +3636,7 @@
       <c r="E26" s="21"/>
       <c r="F26" s="8"/>
     </row>
-    <row r="27" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>25</v>
       </c>
@@ -3732,7 +3646,7 @@
       <c r="E27" s="21"/>
       <c r="F27" s="8"/>
     </row>
-    <row r="28" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>26</v>
       </c>
@@ -3742,7 +3656,7 @@
       <c r="E28" s="21"/>
       <c r="F28" s="7"/>
     </row>
-    <row r="29" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>27</v>
       </c>
@@ -3752,7 +3666,7 @@
       <c r="E29" s="21"/>
       <c r="F29" s="8"/>
     </row>
-    <row r="30" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>28</v>
       </c>
@@ -3762,7 +3676,7 @@
       <c r="E30" s="21"/>
       <c r="F30" s="8"/>
     </row>
-    <row r="31" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>29</v>
       </c>
@@ -3772,7 +3686,7 @@
       <c r="E31" s="21"/>
       <c r="F31" s="7"/>
     </row>
-    <row r="32" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>30</v>
       </c>
@@ -3782,7 +3696,7 @@
       <c r="E32" s="21"/>
       <c r="F32" s="8"/>
     </row>
-    <row r="33" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>31</v>
       </c>
@@ -3792,7 +3706,7 @@
       <c r="E33" s="21"/>
       <c r="F33" s="8"/>
     </row>
-    <row r="34" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <v>32</v>
       </c>
@@ -3802,7 +3716,7 @@
       <c r="E34" s="21"/>
       <c r="F34" s="7"/>
     </row>
-    <row r="35" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>33</v>
       </c>
@@ -3812,7 +3726,7 @@
       <c r="E35" s="21"/>
       <c r="F35" s="8"/>
     </row>
-    <row r="36" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>34</v>
       </c>
@@ -3822,7 +3736,7 @@
       <c r="E36" s="21"/>
       <c r="F36" s="8"/>
     </row>
-    <row r="37" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>35</v>
       </c>
@@ -3832,7 +3746,7 @@
       <c r="E37" s="21"/>
       <c r="F37" s="7"/>
     </row>
-    <row r="38" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>36</v>
       </c>
@@ -3842,7 +3756,7 @@
       <c r="E38" s="21"/>
       <c r="F38" s="8"/>
     </row>
-    <row r="39" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>37</v>
       </c>
@@ -3852,7 +3766,7 @@
       <c r="E39" s="21"/>
       <c r="F39" s="8"/>
     </row>
-    <row r="40" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>38</v>
       </c>
@@ -3862,7 +3776,7 @@
       <c r="E40" s="21"/>
       <c r="F40" s="7"/>
     </row>
-    <row r="41" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>39</v>
       </c>
@@ -3872,7 +3786,7 @@
       <c r="E41" s="21"/>
       <c r="F41" s="8"/>
     </row>
-    <row r="42" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <v>40</v>
       </c>
@@ -3882,7 +3796,7 @@
       <c r="E42" s="21"/>
       <c r="F42" s="7"/>
     </row>
-    <row r="43" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>41</v>
       </c>
@@ -3892,7 +3806,7 @@
       <c r="E43" s="21"/>
       <c r="F43" s="8"/>
     </row>
-    <row r="44" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <v>42</v>
       </c>
@@ -3902,7 +3816,7 @@
       <c r="E44" s="21"/>
       <c r="F44" s="8"/>
     </row>
-    <row r="45" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>43</v>
       </c>
@@ -3912,7 +3826,7 @@
       <c r="E45" s="21"/>
       <c r="F45" s="7"/>
     </row>
-    <row r="46" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <v>44</v>
       </c>
@@ -3922,7 +3836,7 @@
       <c r="E46" s="21"/>
       <c r="F46" s="8"/>
     </row>
-    <row r="47" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <v>45</v>
       </c>
@@ -3932,7 +3846,7 @@
       <c r="E47" s="21"/>
       <c r="F47" s="8"/>
     </row>
-    <row r="48" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <v>46</v>
       </c>
@@ -3942,7 +3856,7 @@
       <c r="E48" s="21"/>
       <c r="F48" s="7"/>
     </row>
-    <row r="49" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>47</v>
       </c>
@@ -3952,7 +3866,7 @@
       <c r="E49" s="21"/>
       <c r="F49" s="8"/>
     </row>
-    <row r="50" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
         <v>48</v>
       </c>
@@ -3962,7 +3876,7 @@
       <c r="E50" s="21"/>
       <c r="F50" s="7"/>
     </row>
-    <row r="51" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <v>49</v>
       </c>
@@ -3972,7 +3886,7 @@
       <c r="E51" s="21"/>
       <c r="F51" s="8"/>
     </row>
-    <row r="52" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
         <v>50</v>
       </c>
@@ -3982,413 +3896,413 @@
       <c r="E52" s="21"/>
       <c r="F52" s="7"/>
     </row>
-    <row r="53" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="10"/>
       <c r="C53" s="10"/>
       <c r="D53" s="10"/>
       <c r="E53" s="22"/>
       <c r="F53" s="6"/>
     </row>
-    <row r="54" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="10"/>
       <c r="C54" s="10"/>
       <c r="D54" s="10"/>
       <c r="E54" s="22"/>
       <c r="F54" s="6"/>
     </row>
-    <row r="55" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="10"/>
       <c r="C55" s="10"/>
       <c r="D55" s="10"/>
       <c r="E55" s="22"/>
       <c r="F55" s="6"/>
     </row>
-    <row r="56" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="10"/>
       <c r="C56" s="10"/>
       <c r="D56" s="10"/>
       <c r="E56" s="22"/>
       <c r="F56" s="6"/>
     </row>
-    <row r="57" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="10"/>
       <c r="C57" s="10"/>
       <c r="D57" s="10"/>
       <c r="E57" s="22"/>
       <c r="F57" s="6"/>
     </row>
-    <row r="58" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="10"/>
       <c r="C58" s="10"/>
       <c r="D58" s="10"/>
       <c r="E58" s="22"/>
       <c r="F58" s="6"/>
     </row>
-    <row r="59" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="10"/>
       <c r="C59" s="10"/>
       <c r="D59" s="10"/>
       <c r="E59" s="22"/>
       <c r="F59" s="6"/>
     </row>
-    <row r="60" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="10"/>
       <c r="C60" s="10"/>
       <c r="D60" s="10"/>
       <c r="E60" s="22"/>
       <c r="F60" s="6"/>
     </row>
-    <row r="61" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="10"/>
       <c r="C61" s="10"/>
       <c r="D61" s="10"/>
       <c r="E61" s="22"/>
       <c r="F61" s="6"/>
     </row>
-    <row r="62" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="10"/>
       <c r="C62" s="10"/>
       <c r="D62" s="10"/>
       <c r="E62" s="22"/>
       <c r="F62" s="6"/>
     </row>
-    <row r="63" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="10"/>
       <c r="C63" s="10"/>
       <c r="D63" s="10"/>
       <c r="E63" s="22"/>
       <c r="F63" s="6"/>
     </row>
-    <row r="64" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B64" s="10"/>
       <c r="C64" s="10"/>
       <c r="D64" s="10"/>
       <c r="E64" s="22"/>
       <c r="F64" s="6"/>
     </row>
-    <row r="65" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="10"/>
       <c r="C65" s="10"/>
       <c r="D65" s="10"/>
       <c r="E65" s="22"/>
       <c r="F65" s="6"/>
     </row>
-    <row r="66" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="10"/>
       <c r="C66" s="10"/>
       <c r="D66" s="10"/>
       <c r="E66" s="22"/>
       <c r="F66" s="6"/>
     </row>
-    <row r="67" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="10"/>
       <c r="C67" s="10"/>
       <c r="D67" s="10"/>
       <c r="E67" s="22"/>
       <c r="F67" s="6"/>
     </row>
-    <row r="68" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="10"/>
       <c r="C68" s="10"/>
       <c r="D68" s="10"/>
       <c r="E68" s="22"/>
       <c r="F68" s="6"/>
     </row>
-    <row r="69" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B69" s="10"/>
       <c r="C69" s="10"/>
       <c r="D69" s="10"/>
       <c r="E69" s="22"/>
       <c r="F69" s="6"/>
     </row>
-    <row r="70" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="10"/>
       <c r="C70" s="10"/>
       <c r="D70" s="10"/>
       <c r="E70" s="22"/>
       <c r="F70" s="6"/>
     </row>
-    <row r="71" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="10"/>
       <c r="C71" s="10"/>
       <c r="D71" s="10"/>
       <c r="E71" s="22"/>
       <c r="F71" s="6"/>
     </row>
-    <row r="72" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B72" s="10"/>
       <c r="C72" s="10"/>
       <c r="D72" s="10"/>
       <c r="E72" s="22"/>
       <c r="F72" s="6"/>
     </row>
-    <row r="73" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B73" s="10"/>
       <c r="C73" s="10"/>
       <c r="D73" s="10"/>
       <c r="E73" s="22"/>
       <c r="F73" s="6"/>
     </row>
-    <row r="74" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" s="10"/>
       <c r="C74" s="10"/>
       <c r="D74" s="10"/>
       <c r="E74" s="22"/>
       <c r="F74" s="6"/>
     </row>
-    <row r="75" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B75" s="10"/>
       <c r="C75" s="10"/>
       <c r="D75" s="10"/>
       <c r="E75" s="22"/>
       <c r="F75" s="6"/>
     </row>
-    <row r="76" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B76" s="10"/>
       <c r="C76" s="10"/>
       <c r="D76" s="10"/>
       <c r="E76" s="22"/>
       <c r="F76" s="6"/>
     </row>
-    <row r="77" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="10"/>
       <c r="C77" s="10"/>
       <c r="D77" s="10"/>
       <c r="E77" s="22"/>
       <c r="F77" s="6"/>
     </row>
-    <row r="78" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B78" s="10"/>
       <c r="C78" s="10"/>
       <c r="D78" s="10"/>
       <c r="E78" s="22"/>
       <c r="F78" s="6"/>
     </row>
-    <row r="79" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B79" s="10"/>
       <c r="C79" s="10"/>
       <c r="D79" s="10"/>
       <c r="E79" s="22"/>
       <c r="F79" s="6"/>
     </row>
-    <row r="80" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B80" s="10"/>
       <c r="C80" s="10"/>
       <c r="D80" s="10"/>
       <c r="E80" s="22"/>
       <c r="F80" s="6"/>
     </row>
-    <row r="81" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B81" s="10"/>
       <c r="C81" s="10"/>
       <c r="D81" s="10"/>
       <c r="E81" s="22"/>
       <c r="F81" s="6"/>
     </row>
-    <row r="82" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" s="10"/>
       <c r="C82" s="10"/>
       <c r="D82" s="10"/>
       <c r="E82" s="22"/>
       <c r="F82" s="6"/>
     </row>
-    <row r="83" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B83" s="10"/>
       <c r="C83" s="10"/>
       <c r="D83" s="10"/>
       <c r="E83" s="22"/>
       <c r="F83" s="6"/>
     </row>
-    <row r="84" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B84" s="10"/>
       <c r="C84" s="10"/>
       <c r="D84" s="10"/>
       <c r="E84" s="22"/>
       <c r="F84" s="6"/>
     </row>
-    <row r="85" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B85" s="10"/>
       <c r="C85" s="10"/>
       <c r="D85" s="10"/>
       <c r="E85" s="22"/>
       <c r="F85" s="6"/>
     </row>
-    <row r="86" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B86" s="10"/>
       <c r="C86" s="10"/>
       <c r="D86" s="10"/>
       <c r="E86" s="22"/>
       <c r="F86" s="6"/>
     </row>
-    <row r="87" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B87" s="10"/>
       <c r="C87" s="10"/>
       <c r="D87" s="10"/>
       <c r="E87" s="22"/>
       <c r="F87" s="6"/>
     </row>
-    <row r="88" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B88" s="10"/>
       <c r="C88" s="10"/>
       <c r="D88" s="10"/>
       <c r="E88" s="22"/>
       <c r="F88" s="6"/>
     </row>
-    <row r="89" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B89" s="10"/>
       <c r="C89" s="10"/>
       <c r="D89" s="10"/>
       <c r="E89" s="22"/>
       <c r="F89" s="6"/>
     </row>
-    <row r="90" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B90" s="10"/>
       <c r="C90" s="10"/>
       <c r="D90" s="10"/>
       <c r="E90" s="22"/>
       <c r="F90" s="6"/>
     </row>
-    <row r="91" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B91" s="10"/>
       <c r="C91" s="10"/>
       <c r="D91" s="10"/>
       <c r="E91" s="22"/>
       <c r="F91" s="6"/>
     </row>
-    <row r="92" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B92" s="10"/>
       <c r="C92" s="10"/>
       <c r="D92" s="10"/>
       <c r="E92" s="22"/>
       <c r="F92" s="6"/>
     </row>
-    <row r="93" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B93" s="10"/>
       <c r="C93" s="10"/>
       <c r="D93" s="10"/>
       <c r="E93" s="22"/>
       <c r="F93" s="6"/>
     </row>
-    <row r="94" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B94" s="10"/>
       <c r="C94" s="10"/>
       <c r="D94" s="10"/>
       <c r="E94" s="22"/>
       <c r="F94" s="6"/>
     </row>
-    <row r="95" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B95" s="10"/>
       <c r="C95" s="10"/>
       <c r="D95" s="10"/>
       <c r="E95" s="22"/>
       <c r="F95" s="6"/>
     </row>
-    <row r="96" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B96" s="10"/>
       <c r="C96" s="10"/>
       <c r="D96" s="10"/>
       <c r="E96" s="22"/>
       <c r="F96" s="6"/>
     </row>
-    <row r="97" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B97" s="10"/>
       <c r="C97" s="10"/>
       <c r="D97" s="10"/>
       <c r="E97" s="22"/>
       <c r="F97" s="6"/>
     </row>
-    <row r="98" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B98" s="10"/>
       <c r="C98" s="10"/>
       <c r="D98" s="10"/>
       <c r="E98" s="22"/>
       <c r="F98" s="6"/>
     </row>
-    <row r="99" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B99" s="10"/>
       <c r="C99" s="10"/>
       <c r="D99" s="10"/>
       <c r="E99" s="22"/>
       <c r="F99" s="6"/>
     </row>
-    <row r="100" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B100" s="10"/>
       <c r="C100" s="10"/>
       <c r="D100" s="10"/>
       <c r="E100" s="22"/>
       <c r="F100" s="6"/>
     </row>
-    <row r="101" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B101" s="10"/>
       <c r="C101" s="10"/>
       <c r="D101" s="10"/>
       <c r="E101" s="22"/>
       <c r="F101" s="6"/>
     </row>
-    <row r="102" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B102" s="10"/>
       <c r="C102" s="10"/>
       <c r="D102" s="10"/>
       <c r="E102" s="22"/>
       <c r="F102" s="6"/>
     </row>
-    <row r="103" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B103" s="10"/>
       <c r="C103" s="10"/>
       <c r="D103" s="10"/>
       <c r="E103" s="22"/>
       <c r="F103" s="6"/>
     </row>
-    <row r="104" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B104" s="10"/>
       <c r="C104" s="10"/>
       <c r="D104" s="10"/>
       <c r="E104" s="22"/>
       <c r="F104" s="6"/>
     </row>
-    <row r="105" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B105" s="10"/>
       <c r="C105" s="10"/>
       <c r="D105" s="10"/>
       <c r="E105" s="22"/>
       <c r="F105" s="6"/>
     </row>
-    <row r="106" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B106" s="10"/>
       <c r="C106" s="10"/>
       <c r="D106" s="10"/>
       <c r="E106" s="22"/>
       <c r="F106" s="6"/>
     </row>
-    <row r="107" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B107" s="10"/>
       <c r="C107" s="10"/>
       <c r="D107" s="10"/>
       <c r="E107" s="22"/>
       <c r="F107" s="6"/>
     </row>
-    <row r="108" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B108" s="10"/>
       <c r="C108" s="10"/>
       <c r="D108" s="10"/>
       <c r="E108" s="22"/>
       <c r="F108" s="6"/>
     </row>
-    <row r="109" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B109" s="10"/>
       <c r="C109" s="10"/>
       <c r="D109" s="10"/>
       <c r="E109" s="22"/>
       <c r="F109" s="6"/>
     </row>
-    <row r="110" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B110" s="10"/>
       <c r="C110" s="10"/>
       <c r="D110" s="10"/>
       <c r="E110" s="22"/>
       <c r="F110" s="6"/>
     </row>
-    <row r="111" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B111" s="10"/>
       <c r="C111" s="10"/>
       <c r="D111" s="10"/>
@@ -4408,29 +4322,29 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5B25C37-05C0-42A6-9331-8C0E946EB5B7}">
   <dimension ref="A1:I111"/>
-  <sheetFormatPr defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.03515625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.125" style="5" customWidth="1"/>
-    <col min="2" max="4" width="13.75" style="5" customWidth="1"/>
-    <col min="5" max="5" width="75.625" style="23" customWidth="1"/>
-    <col min="6" max="6" width="75.625" style="11" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="10.1484375" style="5" customWidth="1"/>
+    <col min="2" max="4" width="13.73828125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="75.6328125" style="23" customWidth="1"/>
+    <col min="6" max="6" width="75.6328125" style="11" customWidth="1"/>
+    <col min="7" max="16384" width="9.03515625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="44" t="s">
-        <v>34</v>
-      </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
+    <row r="1" spans="1:9" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="43" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
       <c r="G1" s="19"/>
       <c r="H1" s="19"/>
       <c r="I1" s="19"/>
     </row>
-    <row r="2" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -4438,7 +4352,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D2" s="18" t="s">
         <v>9</v>
@@ -4450,7 +4364,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>1</v>
       </c>
@@ -4460,7 +4374,7 @@
       <c r="E3" s="21"/>
       <c r="F3" s="7"/>
     </row>
-    <row r="4" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>2</v>
       </c>
@@ -4470,7 +4384,7 @@
       <c r="E4" s="21"/>
       <c r="F4" s="8"/>
     </row>
-    <row r="5" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>3</v>
       </c>
@@ -4480,7 +4394,7 @@
       <c r="E5" s="21"/>
       <c r="F5" s="7"/>
     </row>
-    <row r="6" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>4</v>
       </c>
@@ -4490,7 +4404,7 @@
       <c r="E6" s="21"/>
       <c r="F6" s="8"/>
     </row>
-    <row r="7" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>5</v>
       </c>
@@ -4500,7 +4414,7 @@
       <c r="E7" s="21"/>
       <c r="F7" s="7"/>
     </row>
-    <row r="8" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>6</v>
       </c>
@@ -4510,7 +4424,7 @@
       <c r="E8" s="21"/>
       <c r="F8" s="8"/>
     </row>
-    <row r="9" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>7</v>
       </c>
@@ -4520,7 +4434,7 @@
       <c r="E9" s="24"/>
       <c r="F9" s="7"/>
     </row>
-    <row r="10" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>8</v>
       </c>
@@ -4530,7 +4444,7 @@
       <c r="E10" s="21"/>
       <c r="F10" s="8"/>
     </row>
-    <row r="11" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>9</v>
       </c>
@@ -4540,7 +4454,7 @@
       <c r="E11" s="21"/>
       <c r="F11" s="7"/>
     </row>
-    <row r="12" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>10</v>
       </c>
@@ -4550,7 +4464,7 @@
       <c r="E12" s="21"/>
       <c r="F12" s="8"/>
     </row>
-    <row r="13" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>11</v>
       </c>
@@ -4560,7 +4474,7 @@
       <c r="E13" s="21"/>
       <c r="F13" s="7"/>
     </row>
-    <row r="14" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>12</v>
       </c>
@@ -4570,7 +4484,7 @@
       <c r="E14" s="21"/>
       <c r="F14" s="8"/>
     </row>
-    <row r="15" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>13</v>
       </c>
@@ -4580,7 +4494,7 @@
       <c r="E15" s="21"/>
       <c r="F15" s="7"/>
     </row>
-    <row r="16" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>14</v>
       </c>
@@ -4590,7 +4504,7 @@
       <c r="E16" s="21"/>
       <c r="F16" s="8"/>
     </row>
-    <row r="17" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>15</v>
       </c>
@@ -4600,7 +4514,7 @@
       <c r="E17" s="21"/>
       <c r="F17" s="7"/>
     </row>
-    <row r="18" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>16</v>
       </c>
@@ -4610,7 +4524,7 @@
       <c r="E18" s="21"/>
       <c r="F18" s="8"/>
     </row>
-    <row r="19" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>17</v>
       </c>
@@ -4620,7 +4534,7 @@
       <c r="E19" s="21"/>
       <c r="F19" s="7"/>
     </row>
-    <row r="20" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>18</v>
       </c>
@@ -4630,7 +4544,7 @@
       <c r="E20" s="21"/>
       <c r="F20" s="8"/>
     </row>
-    <row r="21" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>19</v>
       </c>
@@ -4640,7 +4554,7 @@
       <c r="E21" s="21"/>
       <c r="F21" s="8"/>
     </row>
-    <row r="22" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>20</v>
       </c>
@@ -4650,7 +4564,7 @@
       <c r="E22" s="21"/>
       <c r="F22" s="7"/>
     </row>
-    <row r="23" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>21</v>
       </c>
@@ -4660,7 +4574,7 @@
       <c r="E23" s="21"/>
       <c r="F23" s="8"/>
     </row>
-    <row r="24" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>22</v>
       </c>
@@ -4670,7 +4584,7 @@
       <c r="E24" s="21"/>
       <c r="F24" s="8"/>
     </row>
-    <row r="25" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>23</v>
       </c>
@@ -4680,7 +4594,7 @@
       <c r="E25" s="21"/>
       <c r="F25" s="7"/>
     </row>
-    <row r="26" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>24</v>
       </c>
@@ -4690,7 +4604,7 @@
       <c r="E26" s="21"/>
       <c r="F26" s="8"/>
     </row>
-    <row r="27" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>25</v>
       </c>
@@ -4700,7 +4614,7 @@
       <c r="E27" s="21"/>
       <c r="F27" s="8"/>
     </row>
-    <row r="28" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>26</v>
       </c>
@@ -4710,7 +4624,7 @@
       <c r="E28" s="21"/>
       <c r="F28" s="7"/>
     </row>
-    <row r="29" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>27</v>
       </c>
@@ -4720,7 +4634,7 @@
       <c r="E29" s="21"/>
       <c r="F29" s="8"/>
     </row>
-    <row r="30" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>28</v>
       </c>
@@ -4730,7 +4644,7 @@
       <c r="E30" s="21"/>
       <c r="F30" s="8"/>
     </row>
-    <row r="31" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>29</v>
       </c>
@@ -4740,7 +4654,7 @@
       <c r="E31" s="21"/>
       <c r="F31" s="7"/>
     </row>
-    <row r="32" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>30</v>
       </c>
@@ -4750,7 +4664,7 @@
       <c r="E32" s="21"/>
       <c r="F32" s="8"/>
     </row>
-    <row r="33" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>31</v>
       </c>
@@ -4760,7 +4674,7 @@
       <c r="E33" s="21"/>
       <c r="F33" s="8"/>
     </row>
-    <row r="34" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <v>32</v>
       </c>
@@ -4770,7 +4684,7 @@
       <c r="E34" s="21"/>
       <c r="F34" s="7"/>
     </row>
-    <row r="35" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>33</v>
       </c>
@@ -4780,7 +4694,7 @@
       <c r="E35" s="21"/>
       <c r="F35" s="8"/>
     </row>
-    <row r="36" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>34</v>
       </c>
@@ -4790,7 +4704,7 @@
       <c r="E36" s="21"/>
       <c r="F36" s="8"/>
     </row>
-    <row r="37" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>35</v>
       </c>
@@ -4800,7 +4714,7 @@
       <c r="E37" s="21"/>
       <c r="F37" s="7"/>
     </row>
-    <row r="38" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>36</v>
       </c>
@@ -4810,7 +4724,7 @@
       <c r="E38" s="21"/>
       <c r="F38" s="8"/>
     </row>
-    <row r="39" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>37</v>
       </c>
@@ -4820,7 +4734,7 @@
       <c r="E39" s="21"/>
       <c r="F39" s="8"/>
     </row>
-    <row r="40" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>38</v>
       </c>
@@ -4830,7 +4744,7 @@
       <c r="E40" s="21"/>
       <c r="F40" s="7"/>
     </row>
-    <row r="41" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>39</v>
       </c>
@@ -4840,7 +4754,7 @@
       <c r="E41" s="21"/>
       <c r="F41" s="8"/>
     </row>
-    <row r="42" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <v>40</v>
       </c>
@@ -4850,7 +4764,7 @@
       <c r="E42" s="21"/>
       <c r="F42" s="7"/>
     </row>
-    <row r="43" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>41</v>
       </c>
@@ -4860,7 +4774,7 @@
       <c r="E43" s="21"/>
       <c r="F43" s="8"/>
     </row>
-    <row r="44" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <v>42</v>
       </c>
@@ -4870,7 +4784,7 @@
       <c r="E44" s="21"/>
       <c r="F44" s="8"/>
     </row>
-    <row r="45" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>43</v>
       </c>
@@ -4880,7 +4794,7 @@
       <c r="E45" s="21"/>
       <c r="F45" s="7"/>
     </row>
-    <row r="46" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <v>44</v>
       </c>
@@ -4890,7 +4804,7 @@
       <c r="E46" s="21"/>
       <c r="F46" s="8"/>
     </row>
-    <row r="47" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <v>45</v>
       </c>
@@ -4900,7 +4814,7 @@
       <c r="E47" s="21"/>
       <c r="F47" s="8"/>
     </row>
-    <row r="48" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <v>46</v>
       </c>
@@ -4910,7 +4824,7 @@
       <c r="E48" s="21"/>
       <c r="F48" s="7"/>
     </row>
-    <row r="49" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>47</v>
       </c>
@@ -4920,7 +4834,7 @@
       <c r="E49" s="21"/>
       <c r="F49" s="8"/>
     </row>
-    <row r="50" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
         <v>48</v>
       </c>
@@ -4930,7 +4844,7 @@
       <c r="E50" s="21"/>
       <c r="F50" s="7"/>
     </row>
-    <row r="51" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <v>49</v>
       </c>
@@ -4940,7 +4854,7 @@
       <c r="E51" s="21"/>
       <c r="F51" s="8"/>
     </row>
-    <row r="52" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
         <v>50</v>
       </c>
@@ -4950,413 +4864,413 @@
       <c r="E52" s="21"/>
       <c r="F52" s="7"/>
     </row>
-    <row r="53" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="10"/>
       <c r="C53" s="10"/>
       <c r="D53" s="10"/>
       <c r="E53" s="22"/>
       <c r="F53" s="6"/>
     </row>
-    <row r="54" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="10"/>
       <c r="C54" s="10"/>
       <c r="D54" s="10"/>
       <c r="E54" s="22"/>
       <c r="F54" s="6"/>
     </row>
-    <row r="55" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="10"/>
       <c r="C55" s="10"/>
       <c r="D55" s="10"/>
       <c r="E55" s="22"/>
       <c r="F55" s="6"/>
     </row>
-    <row r="56" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="10"/>
       <c r="C56" s="10"/>
       <c r="D56" s="10"/>
       <c r="E56" s="22"/>
       <c r="F56" s="6"/>
     </row>
-    <row r="57" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="10"/>
       <c r="C57" s="10"/>
       <c r="D57" s="10"/>
       <c r="E57" s="22"/>
       <c r="F57" s="6"/>
     </row>
-    <row r="58" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="10"/>
       <c r="C58" s="10"/>
       <c r="D58" s="10"/>
       <c r="E58" s="22"/>
       <c r="F58" s="6"/>
     </row>
-    <row r="59" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="10"/>
       <c r="C59" s="10"/>
       <c r="D59" s="10"/>
       <c r="E59" s="22"/>
       <c r="F59" s="6"/>
     </row>
-    <row r="60" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="10"/>
       <c r="C60" s="10"/>
       <c r="D60" s="10"/>
       <c r="E60" s="22"/>
       <c r="F60" s="6"/>
     </row>
-    <row r="61" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="10"/>
       <c r="C61" s="10"/>
       <c r="D61" s="10"/>
       <c r="E61" s="22"/>
       <c r="F61" s="6"/>
     </row>
-    <row r="62" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="10"/>
       <c r="C62" s="10"/>
       <c r="D62" s="10"/>
       <c r="E62" s="22"/>
       <c r="F62" s="6"/>
     </row>
-    <row r="63" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="10"/>
       <c r="C63" s="10"/>
       <c r="D63" s="10"/>
       <c r="E63" s="22"/>
       <c r="F63" s="6"/>
     </row>
-    <row r="64" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B64" s="10"/>
       <c r="C64" s="10"/>
       <c r="D64" s="10"/>
       <c r="E64" s="22"/>
       <c r="F64" s="6"/>
     </row>
-    <row r="65" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="10"/>
       <c r="C65" s="10"/>
       <c r="D65" s="10"/>
       <c r="E65" s="22"/>
       <c r="F65" s="6"/>
     </row>
-    <row r="66" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="10"/>
       <c r="C66" s="10"/>
       <c r="D66" s="10"/>
       <c r="E66" s="22"/>
       <c r="F66" s="6"/>
     </row>
-    <row r="67" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="10"/>
       <c r="C67" s="10"/>
       <c r="D67" s="10"/>
       <c r="E67" s="22"/>
       <c r="F67" s="6"/>
     </row>
-    <row r="68" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="10"/>
       <c r="C68" s="10"/>
       <c r="D68" s="10"/>
       <c r="E68" s="22"/>
       <c r="F68" s="6"/>
     </row>
-    <row r="69" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B69" s="10"/>
       <c r="C69" s="10"/>
       <c r="D69" s="10"/>
       <c r="E69" s="22"/>
       <c r="F69" s="6"/>
     </row>
-    <row r="70" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="10"/>
       <c r="C70" s="10"/>
       <c r="D70" s="10"/>
       <c r="E70" s="22"/>
       <c r="F70" s="6"/>
     </row>
-    <row r="71" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="10"/>
       <c r="C71" s="10"/>
       <c r="D71" s="10"/>
       <c r="E71" s="22"/>
       <c r="F71" s="6"/>
     </row>
-    <row r="72" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B72" s="10"/>
       <c r="C72" s="10"/>
       <c r="D72" s="10"/>
       <c r="E72" s="22"/>
       <c r="F72" s="6"/>
     </row>
-    <row r="73" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B73" s="10"/>
       <c r="C73" s="10"/>
       <c r="D73" s="10"/>
       <c r="E73" s="22"/>
       <c r="F73" s="6"/>
     </row>
-    <row r="74" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" s="10"/>
       <c r="C74" s="10"/>
       <c r="D74" s="10"/>
       <c r="E74" s="22"/>
       <c r="F74" s="6"/>
     </row>
-    <row r="75" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B75" s="10"/>
       <c r="C75" s="10"/>
       <c r="D75" s="10"/>
       <c r="E75" s="22"/>
       <c r="F75" s="6"/>
     </row>
-    <row r="76" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B76" s="10"/>
       <c r="C76" s="10"/>
       <c r="D76" s="10"/>
       <c r="E76" s="22"/>
       <c r="F76" s="6"/>
     </row>
-    <row r="77" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="10"/>
       <c r="C77" s="10"/>
       <c r="D77" s="10"/>
       <c r="E77" s="22"/>
       <c r="F77" s="6"/>
     </row>
-    <row r="78" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B78" s="10"/>
       <c r="C78" s="10"/>
       <c r="D78" s="10"/>
       <c r="E78" s="22"/>
       <c r="F78" s="6"/>
     </row>
-    <row r="79" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B79" s="10"/>
       <c r="C79" s="10"/>
       <c r="D79" s="10"/>
       <c r="E79" s="22"/>
       <c r="F79" s="6"/>
     </row>
-    <row r="80" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B80" s="10"/>
       <c r="C80" s="10"/>
       <c r="D80" s="10"/>
       <c r="E80" s="22"/>
       <c r="F80" s="6"/>
     </row>
-    <row r="81" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B81" s="10"/>
       <c r="C81" s="10"/>
       <c r="D81" s="10"/>
       <c r="E81" s="22"/>
       <c r="F81" s="6"/>
     </row>
-    <row r="82" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" s="10"/>
       <c r="C82" s="10"/>
       <c r="D82" s="10"/>
       <c r="E82" s="22"/>
       <c r="F82" s="6"/>
     </row>
-    <row r="83" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B83" s="10"/>
       <c r="C83" s="10"/>
       <c r="D83" s="10"/>
       <c r="E83" s="22"/>
       <c r="F83" s="6"/>
     </row>
-    <row r="84" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B84" s="10"/>
       <c r="C84" s="10"/>
       <c r="D84" s="10"/>
       <c r="E84" s="22"/>
       <c r="F84" s="6"/>
     </row>
-    <row r="85" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B85" s="10"/>
       <c r="C85" s="10"/>
       <c r="D85" s="10"/>
       <c r="E85" s="22"/>
       <c r="F85" s="6"/>
     </row>
-    <row r="86" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B86" s="10"/>
       <c r="C86" s="10"/>
       <c r="D86" s="10"/>
       <c r="E86" s="22"/>
       <c r="F86" s="6"/>
     </row>
-    <row r="87" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B87" s="10"/>
       <c r="C87" s="10"/>
       <c r="D87" s="10"/>
       <c r="E87" s="22"/>
       <c r="F87" s="6"/>
     </row>
-    <row r="88" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B88" s="10"/>
       <c r="C88" s="10"/>
       <c r="D88" s="10"/>
       <c r="E88" s="22"/>
       <c r="F88" s="6"/>
     </row>
-    <row r="89" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B89" s="10"/>
       <c r="C89" s="10"/>
       <c r="D89" s="10"/>
       <c r="E89" s="22"/>
       <c r="F89" s="6"/>
     </row>
-    <row r="90" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B90" s="10"/>
       <c r="C90" s="10"/>
       <c r="D90" s="10"/>
       <c r="E90" s="22"/>
       <c r="F90" s="6"/>
     </row>
-    <row r="91" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B91" s="10"/>
       <c r="C91" s="10"/>
       <c r="D91" s="10"/>
       <c r="E91" s="22"/>
       <c r="F91" s="6"/>
     </row>
-    <row r="92" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B92" s="10"/>
       <c r="C92" s="10"/>
       <c r="D92" s="10"/>
       <c r="E92" s="22"/>
       <c r="F92" s="6"/>
     </row>
-    <row r="93" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B93" s="10"/>
       <c r="C93" s="10"/>
       <c r="D93" s="10"/>
       <c r="E93" s="22"/>
       <c r="F93" s="6"/>
     </row>
-    <row r="94" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B94" s="10"/>
       <c r="C94" s="10"/>
       <c r="D94" s="10"/>
       <c r="E94" s="22"/>
       <c r="F94" s="6"/>
     </row>
-    <row r="95" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B95" s="10"/>
       <c r="C95" s="10"/>
       <c r="D95" s="10"/>
       <c r="E95" s="22"/>
       <c r="F95" s="6"/>
     </row>
-    <row r="96" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B96" s="10"/>
       <c r="C96" s="10"/>
       <c r="D96" s="10"/>
       <c r="E96" s="22"/>
       <c r="F96" s="6"/>
     </row>
-    <row r="97" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B97" s="10"/>
       <c r="C97" s="10"/>
       <c r="D97" s="10"/>
       <c r="E97" s="22"/>
       <c r="F97" s="6"/>
     </row>
-    <row r="98" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B98" s="10"/>
       <c r="C98" s="10"/>
       <c r="D98" s="10"/>
       <c r="E98" s="22"/>
       <c r="F98" s="6"/>
     </row>
-    <row r="99" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B99" s="10"/>
       <c r="C99" s="10"/>
       <c r="D99" s="10"/>
       <c r="E99" s="22"/>
       <c r="F99" s="6"/>
     </row>
-    <row r="100" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B100" s="10"/>
       <c r="C100" s="10"/>
       <c r="D100" s="10"/>
       <c r="E100" s="22"/>
       <c r="F100" s="6"/>
     </row>
-    <row r="101" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B101" s="10"/>
       <c r="C101" s="10"/>
       <c r="D101" s="10"/>
       <c r="E101" s="22"/>
       <c r="F101" s="6"/>
     </row>
-    <row r="102" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B102" s="10"/>
       <c r="C102" s="10"/>
       <c r="D102" s="10"/>
       <c r="E102" s="22"/>
       <c r="F102" s="6"/>
     </row>
-    <row r="103" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B103" s="10"/>
       <c r="C103" s="10"/>
       <c r="D103" s="10"/>
       <c r="E103" s="22"/>
       <c r="F103" s="6"/>
     </row>
-    <row r="104" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B104" s="10"/>
       <c r="C104" s="10"/>
       <c r="D104" s="10"/>
       <c r="E104" s="22"/>
       <c r="F104" s="6"/>
     </row>
-    <row r="105" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B105" s="10"/>
       <c r="C105" s="10"/>
       <c r="D105" s="10"/>
       <c r="E105" s="22"/>
       <c r="F105" s="6"/>
     </row>
-    <row r="106" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B106" s="10"/>
       <c r="C106" s="10"/>
       <c r="D106" s="10"/>
       <c r="E106" s="22"/>
       <c r="F106" s="6"/>
     </row>
-    <row r="107" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B107" s="10"/>
       <c r="C107" s="10"/>
       <c r="D107" s="10"/>
       <c r="E107" s="22"/>
       <c r="F107" s="6"/>
     </row>
-    <row r="108" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B108" s="10"/>
       <c r="C108" s="10"/>
       <c r="D108" s="10"/>
       <c r="E108" s="22"/>
       <c r="F108" s="6"/>
     </row>
-    <row r="109" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B109" s="10"/>
       <c r="C109" s="10"/>
       <c r="D109" s="10"/>
       <c r="E109" s="22"/>
       <c r="F109" s="6"/>
     </row>
-    <row r="110" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B110" s="10"/>
       <c r="C110" s="10"/>
       <c r="D110" s="10"/>
       <c r="E110" s="22"/>
       <c r="F110" s="6"/>
     </row>
-    <row r="111" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B111" s="10"/>
       <c r="C111" s="10"/>
       <c r="D111" s="10"/>
@@ -5376,29 +5290,29 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC4F0146-C665-4EDA-A139-58235E77B16D}">
   <dimension ref="A1:I111"/>
-  <sheetFormatPr defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.03515625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.125" style="5" customWidth="1"/>
-    <col min="2" max="4" width="13.75" style="5" customWidth="1"/>
-    <col min="5" max="5" width="75.625" style="23" customWidth="1"/>
-    <col min="6" max="6" width="75.625" style="11" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="10.1484375" style="5" customWidth="1"/>
+    <col min="2" max="4" width="13.73828125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="75.6328125" style="23" customWidth="1"/>
+    <col min="6" max="6" width="75.6328125" style="11" customWidth="1"/>
+    <col min="7" max="16384" width="9.03515625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="44" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
+    <row r="1" spans="1:9" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
       <c r="G1" s="19"/>
       <c r="H1" s="19"/>
       <c r="I1" s="19"/>
     </row>
-    <row r="2" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -5406,7 +5320,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D2" s="18" t="s">
         <v>9</v>
@@ -5418,7 +5332,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>1</v>
       </c>
@@ -5428,7 +5342,7 @@
       <c r="E3" s="21"/>
       <c r="F3" s="7"/>
     </row>
-    <row r="4" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>2</v>
       </c>
@@ -5438,7 +5352,7 @@
       <c r="E4" s="21"/>
       <c r="F4" s="8"/>
     </row>
-    <row r="5" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>3</v>
       </c>
@@ -5448,7 +5362,7 @@
       <c r="E5" s="21"/>
       <c r="F5" s="7"/>
     </row>
-    <row r="6" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>4</v>
       </c>
@@ -5458,7 +5372,7 @@
       <c r="E6" s="21"/>
       <c r="F6" s="8"/>
     </row>
-    <row r="7" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>5</v>
       </c>
@@ -5468,7 +5382,7 @@
       <c r="E7" s="21"/>
       <c r="F7" s="7"/>
     </row>
-    <row r="8" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>6</v>
       </c>
@@ -5478,7 +5392,7 @@
       <c r="E8" s="21"/>
       <c r="F8" s="8"/>
     </row>
-    <row r="9" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>7</v>
       </c>
@@ -5488,7 +5402,7 @@
       <c r="E9" s="24"/>
       <c r="F9" s="7"/>
     </row>
-    <row r="10" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>8</v>
       </c>
@@ -5498,7 +5412,7 @@
       <c r="E10" s="21"/>
       <c r="F10" s="8"/>
     </row>
-    <row r="11" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>9</v>
       </c>
@@ -5508,7 +5422,7 @@
       <c r="E11" s="21"/>
       <c r="F11" s="7"/>
     </row>
-    <row r="12" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>10</v>
       </c>
@@ -5518,7 +5432,7 @@
       <c r="E12" s="21"/>
       <c r="F12" s="8"/>
     </row>
-    <row r="13" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>11</v>
       </c>
@@ -5528,7 +5442,7 @@
       <c r="E13" s="21"/>
       <c r="F13" s="7"/>
     </row>
-    <row r="14" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>12</v>
       </c>
@@ -5538,7 +5452,7 @@
       <c r="E14" s="21"/>
       <c r="F14" s="8"/>
     </row>
-    <row r="15" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>13</v>
       </c>
@@ -5548,7 +5462,7 @@
       <c r="E15" s="21"/>
       <c r="F15" s="7"/>
     </row>
-    <row r="16" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>14</v>
       </c>
@@ -5558,7 +5472,7 @@
       <c r="E16" s="21"/>
       <c r="F16" s="8"/>
     </row>
-    <row r="17" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>15</v>
       </c>
@@ -5568,7 +5482,7 @@
       <c r="E17" s="21"/>
       <c r="F17" s="7"/>
     </row>
-    <row r="18" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>16</v>
       </c>
@@ -5578,7 +5492,7 @@
       <c r="E18" s="21"/>
       <c r="F18" s="8"/>
     </row>
-    <row r="19" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>17</v>
       </c>
@@ -5588,7 +5502,7 @@
       <c r="E19" s="21"/>
       <c r="F19" s="7"/>
     </row>
-    <row r="20" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>18</v>
       </c>
@@ -5598,7 +5512,7 @@
       <c r="E20" s="21"/>
       <c r="F20" s="8"/>
     </row>
-    <row r="21" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>19</v>
       </c>
@@ -5608,7 +5522,7 @@
       <c r="E21" s="21"/>
       <c r="F21" s="8"/>
     </row>
-    <row r="22" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>20</v>
       </c>
@@ -5618,7 +5532,7 @@
       <c r="E22" s="21"/>
       <c r="F22" s="7"/>
     </row>
-    <row r="23" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>21</v>
       </c>
@@ -5628,7 +5542,7 @@
       <c r="E23" s="21"/>
       <c r="F23" s="8"/>
     </row>
-    <row r="24" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>22</v>
       </c>
@@ -5638,7 +5552,7 @@
       <c r="E24" s="21"/>
       <c r="F24" s="8"/>
     </row>
-    <row r="25" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>23</v>
       </c>
@@ -5648,7 +5562,7 @@
       <c r="E25" s="21"/>
       <c r="F25" s="7"/>
     </row>
-    <row r="26" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>24</v>
       </c>
@@ -5658,7 +5572,7 @@
       <c r="E26" s="21"/>
       <c r="F26" s="8"/>
     </row>
-    <row r="27" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>25</v>
       </c>
@@ -5668,7 +5582,7 @@
       <c r="E27" s="21"/>
       <c r="F27" s="8"/>
     </row>
-    <row r="28" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>26</v>
       </c>
@@ -5678,7 +5592,7 @@
       <c r="E28" s="21"/>
       <c r="F28" s="7"/>
     </row>
-    <row r="29" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>27</v>
       </c>
@@ -5688,7 +5602,7 @@
       <c r="E29" s="21"/>
       <c r="F29" s="8"/>
     </row>
-    <row r="30" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>28</v>
       </c>
@@ -5698,7 +5612,7 @@
       <c r="E30" s="21"/>
       <c r="F30" s="8"/>
     </row>
-    <row r="31" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>29</v>
       </c>
@@ -5708,7 +5622,7 @@
       <c r="E31" s="21"/>
       <c r="F31" s="7"/>
     </row>
-    <row r="32" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>30</v>
       </c>
@@ -5718,7 +5632,7 @@
       <c r="E32" s="21"/>
       <c r="F32" s="8"/>
     </row>
-    <row r="33" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>31</v>
       </c>
@@ -5728,7 +5642,7 @@
       <c r="E33" s="21"/>
       <c r="F33" s="8"/>
     </row>
-    <row r="34" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <v>32</v>
       </c>
@@ -5738,7 +5652,7 @@
       <c r="E34" s="21"/>
       <c r="F34" s="7"/>
     </row>
-    <row r="35" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>33</v>
       </c>
@@ -5748,7 +5662,7 @@
       <c r="E35" s="21"/>
       <c r="F35" s="8"/>
     </row>
-    <row r="36" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>34</v>
       </c>
@@ -5758,7 +5672,7 @@
       <c r="E36" s="21"/>
       <c r="F36" s="8"/>
     </row>
-    <row r="37" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>35</v>
       </c>
@@ -5768,7 +5682,7 @@
       <c r="E37" s="21"/>
       <c r="F37" s="7"/>
     </row>
-    <row r="38" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>36</v>
       </c>
@@ -5778,7 +5692,7 @@
       <c r="E38" s="21"/>
       <c r="F38" s="8"/>
     </row>
-    <row r="39" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>37</v>
       </c>
@@ -5788,7 +5702,7 @@
       <c r="E39" s="21"/>
       <c r="F39" s="8"/>
     </row>
-    <row r="40" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>38</v>
       </c>
@@ -5798,7 +5712,7 @@
       <c r="E40" s="21"/>
       <c r="F40" s="7"/>
     </row>
-    <row r="41" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>39</v>
       </c>
@@ -5808,7 +5722,7 @@
       <c r="E41" s="21"/>
       <c r="F41" s="8"/>
     </row>
-    <row r="42" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <v>40</v>
       </c>
@@ -5818,7 +5732,7 @@
       <c r="E42" s="21"/>
       <c r="F42" s="7"/>
     </row>
-    <row r="43" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>41</v>
       </c>
@@ -5828,7 +5742,7 @@
       <c r="E43" s="21"/>
       <c r="F43" s="8"/>
     </row>
-    <row r="44" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <v>42</v>
       </c>
@@ -5838,7 +5752,7 @@
       <c r="E44" s="21"/>
       <c r="F44" s="8"/>
     </row>
-    <row r="45" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>43</v>
       </c>
@@ -5848,7 +5762,7 @@
       <c r="E45" s="21"/>
       <c r="F45" s="7"/>
     </row>
-    <row r="46" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <v>44</v>
       </c>
@@ -5858,7 +5772,7 @@
       <c r="E46" s="21"/>
       <c r="F46" s="8"/>
     </row>
-    <row r="47" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <v>45</v>
       </c>
@@ -5868,7 +5782,7 @@
       <c r="E47" s="21"/>
       <c r="F47" s="8"/>
     </row>
-    <row r="48" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <v>46</v>
       </c>
@@ -5878,7 +5792,7 @@
       <c r="E48" s="21"/>
       <c r="F48" s="7"/>
     </row>
-    <row r="49" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>47</v>
       </c>
@@ -5888,7 +5802,7 @@
       <c r="E49" s="21"/>
       <c r="F49" s="8"/>
     </row>
-    <row r="50" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
         <v>48</v>
       </c>
@@ -5898,7 +5812,7 @@
       <c r="E50" s="21"/>
       <c r="F50" s="7"/>
     </row>
-    <row r="51" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <v>49</v>
       </c>
@@ -5908,7 +5822,7 @@
       <c r="E51" s="21"/>
       <c r="F51" s="8"/>
     </row>
-    <row r="52" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
         <v>50</v>
       </c>
@@ -5918,413 +5832,413 @@
       <c r="E52" s="21"/>
       <c r="F52" s="7"/>
     </row>
-    <row r="53" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="10"/>
       <c r="C53" s="10"/>
       <c r="D53" s="10"/>
       <c r="E53" s="22"/>
       <c r="F53" s="6"/>
     </row>
-    <row r="54" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="10"/>
       <c r="C54" s="10"/>
       <c r="D54" s="10"/>
       <c r="E54" s="22"/>
       <c r="F54" s="6"/>
     </row>
-    <row r="55" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="10"/>
       <c r="C55" s="10"/>
       <c r="D55" s="10"/>
       <c r="E55" s="22"/>
       <c r="F55" s="6"/>
     </row>
-    <row r="56" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="10"/>
       <c r="C56" s="10"/>
       <c r="D56" s="10"/>
       <c r="E56" s="22"/>
       <c r="F56" s="6"/>
     </row>
-    <row r="57" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="10"/>
       <c r="C57" s="10"/>
       <c r="D57" s="10"/>
       <c r="E57" s="22"/>
       <c r="F57" s="6"/>
     </row>
-    <row r="58" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="10"/>
       <c r="C58" s="10"/>
       <c r="D58" s="10"/>
       <c r="E58" s="22"/>
       <c r="F58" s="6"/>
     </row>
-    <row r="59" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="10"/>
       <c r="C59" s="10"/>
       <c r="D59" s="10"/>
       <c r="E59" s="22"/>
       <c r="F59" s="6"/>
     </row>
-    <row r="60" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="10"/>
       <c r="C60" s="10"/>
       <c r="D60" s="10"/>
       <c r="E60" s="22"/>
       <c r="F60" s="6"/>
     </row>
-    <row r="61" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="10"/>
       <c r="C61" s="10"/>
       <c r="D61" s="10"/>
       <c r="E61" s="22"/>
       <c r="F61" s="6"/>
     </row>
-    <row r="62" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="10"/>
       <c r="C62" s="10"/>
       <c r="D62" s="10"/>
       <c r="E62" s="22"/>
       <c r="F62" s="6"/>
     </row>
-    <row r="63" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="10"/>
       <c r="C63" s="10"/>
       <c r="D63" s="10"/>
       <c r="E63" s="22"/>
       <c r="F63" s="6"/>
     </row>
-    <row r="64" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B64" s="10"/>
       <c r="C64" s="10"/>
       <c r="D64" s="10"/>
       <c r="E64" s="22"/>
       <c r="F64" s="6"/>
     </row>
-    <row r="65" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="10"/>
       <c r="C65" s="10"/>
       <c r="D65" s="10"/>
       <c r="E65" s="22"/>
       <c r="F65" s="6"/>
     </row>
-    <row r="66" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="10"/>
       <c r="C66" s="10"/>
       <c r="D66" s="10"/>
       <c r="E66" s="22"/>
       <c r="F66" s="6"/>
     </row>
-    <row r="67" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="10"/>
       <c r="C67" s="10"/>
       <c r="D67" s="10"/>
       <c r="E67" s="22"/>
       <c r="F67" s="6"/>
     </row>
-    <row r="68" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="10"/>
       <c r="C68" s="10"/>
       <c r="D68" s="10"/>
       <c r="E68" s="22"/>
       <c r="F68" s="6"/>
     </row>
-    <row r="69" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B69" s="10"/>
       <c r="C69" s="10"/>
       <c r="D69" s="10"/>
       <c r="E69" s="22"/>
       <c r="F69" s="6"/>
     </row>
-    <row r="70" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="10"/>
       <c r="C70" s="10"/>
       <c r="D70" s="10"/>
       <c r="E70" s="22"/>
       <c r="F70" s="6"/>
     </row>
-    <row r="71" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="10"/>
       <c r="C71" s="10"/>
       <c r="D71" s="10"/>
       <c r="E71" s="22"/>
       <c r="F71" s="6"/>
     </row>
-    <row r="72" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B72" s="10"/>
       <c r="C72" s="10"/>
       <c r="D72" s="10"/>
       <c r="E72" s="22"/>
       <c r="F72" s="6"/>
     </row>
-    <row r="73" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B73" s="10"/>
       <c r="C73" s="10"/>
       <c r="D73" s="10"/>
       <c r="E73" s="22"/>
       <c r="F73" s="6"/>
     </row>
-    <row r="74" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" s="10"/>
       <c r="C74" s="10"/>
       <c r="D74" s="10"/>
       <c r="E74" s="22"/>
       <c r="F74" s="6"/>
     </row>
-    <row r="75" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B75" s="10"/>
       <c r="C75" s="10"/>
       <c r="D75" s="10"/>
       <c r="E75" s="22"/>
       <c r="F75" s="6"/>
     </row>
-    <row r="76" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B76" s="10"/>
       <c r="C76" s="10"/>
       <c r="D76" s="10"/>
       <c r="E76" s="22"/>
       <c r="F76" s="6"/>
     </row>
-    <row r="77" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="10"/>
       <c r="C77" s="10"/>
       <c r="D77" s="10"/>
       <c r="E77" s="22"/>
       <c r="F77" s="6"/>
     </row>
-    <row r="78" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B78" s="10"/>
       <c r="C78" s="10"/>
       <c r="D78" s="10"/>
       <c r="E78" s="22"/>
       <c r="F78" s="6"/>
     </row>
-    <row r="79" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B79" s="10"/>
       <c r="C79" s="10"/>
       <c r="D79" s="10"/>
       <c r="E79" s="22"/>
       <c r="F79" s="6"/>
     </row>
-    <row r="80" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B80" s="10"/>
       <c r="C80" s="10"/>
       <c r="D80" s="10"/>
       <c r="E80" s="22"/>
       <c r="F80" s="6"/>
     </row>
-    <row r="81" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B81" s="10"/>
       <c r="C81" s="10"/>
       <c r="D81" s="10"/>
       <c r="E81" s="22"/>
       <c r="F81" s="6"/>
     </row>
-    <row r="82" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" s="10"/>
       <c r="C82" s="10"/>
       <c r="D82" s="10"/>
       <c r="E82" s="22"/>
       <c r="F82" s="6"/>
     </row>
-    <row r="83" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B83" s="10"/>
       <c r="C83" s="10"/>
       <c r="D83" s="10"/>
       <c r="E83" s="22"/>
       <c r="F83" s="6"/>
     </row>
-    <row r="84" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B84" s="10"/>
       <c r="C84" s="10"/>
       <c r="D84" s="10"/>
       <c r="E84" s="22"/>
       <c r="F84" s="6"/>
     </row>
-    <row r="85" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B85" s="10"/>
       <c r="C85" s="10"/>
       <c r="D85" s="10"/>
       <c r="E85" s="22"/>
       <c r="F85" s="6"/>
     </row>
-    <row r="86" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B86" s="10"/>
       <c r="C86" s="10"/>
       <c r="D86" s="10"/>
       <c r="E86" s="22"/>
       <c r="F86" s="6"/>
     </row>
-    <row r="87" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B87" s="10"/>
       <c r="C87" s="10"/>
       <c r="D87" s="10"/>
       <c r="E87" s="22"/>
       <c r="F87" s="6"/>
     </row>
-    <row r="88" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B88" s="10"/>
       <c r="C88" s="10"/>
       <c r="D88" s="10"/>
       <c r="E88" s="22"/>
       <c r="F88" s="6"/>
     </row>
-    <row r="89" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B89" s="10"/>
       <c r="C89" s="10"/>
       <c r="D89" s="10"/>
       <c r="E89" s="22"/>
       <c r="F89" s="6"/>
     </row>
-    <row r="90" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B90" s="10"/>
       <c r="C90" s="10"/>
       <c r="D90" s="10"/>
       <c r="E90" s="22"/>
       <c r="F90" s="6"/>
     </row>
-    <row r="91" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B91" s="10"/>
       <c r="C91" s="10"/>
       <c r="D91" s="10"/>
       <c r="E91" s="22"/>
       <c r="F91" s="6"/>
     </row>
-    <row r="92" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B92" s="10"/>
       <c r="C92" s="10"/>
       <c r="D92" s="10"/>
       <c r="E92" s="22"/>
       <c r="F92" s="6"/>
     </row>
-    <row r="93" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B93" s="10"/>
       <c r="C93" s="10"/>
       <c r="D93" s="10"/>
       <c r="E93" s="22"/>
       <c r="F93" s="6"/>
     </row>
-    <row r="94" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B94" s="10"/>
       <c r="C94" s="10"/>
       <c r="D94" s="10"/>
       <c r="E94" s="22"/>
       <c r="F94" s="6"/>
     </row>
-    <row r="95" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B95" s="10"/>
       <c r="C95" s="10"/>
       <c r="D95" s="10"/>
       <c r="E95" s="22"/>
       <c r="F95" s="6"/>
     </row>
-    <row r="96" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B96" s="10"/>
       <c r="C96" s="10"/>
       <c r="D96" s="10"/>
       <c r="E96" s="22"/>
       <c r="F96" s="6"/>
     </row>
-    <row r="97" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B97" s="10"/>
       <c r="C97" s="10"/>
       <c r="D97" s="10"/>
       <c r="E97" s="22"/>
       <c r="F97" s="6"/>
     </row>
-    <row r="98" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B98" s="10"/>
       <c r="C98" s="10"/>
       <c r="D98" s="10"/>
       <c r="E98" s="22"/>
       <c r="F98" s="6"/>
     </row>
-    <row r="99" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B99" s="10"/>
       <c r="C99" s="10"/>
       <c r="D99" s="10"/>
       <c r="E99" s="22"/>
       <c r="F99" s="6"/>
     </row>
-    <row r="100" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B100" s="10"/>
       <c r="C100" s="10"/>
       <c r="D100" s="10"/>
       <c r="E100" s="22"/>
       <c r="F100" s="6"/>
     </row>
-    <row r="101" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B101" s="10"/>
       <c r="C101" s="10"/>
       <c r="D101" s="10"/>
       <c r="E101" s="22"/>
       <c r="F101" s="6"/>
     </row>
-    <row r="102" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B102" s="10"/>
       <c r="C102" s="10"/>
       <c r="D102" s="10"/>
       <c r="E102" s="22"/>
       <c r="F102" s="6"/>
     </row>
-    <row r="103" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B103" s="10"/>
       <c r="C103" s="10"/>
       <c r="D103" s="10"/>
       <c r="E103" s="22"/>
       <c r="F103" s="6"/>
     </row>
-    <row r="104" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B104" s="10"/>
       <c r="C104" s="10"/>
       <c r="D104" s="10"/>
       <c r="E104" s="22"/>
       <c r="F104" s="6"/>
     </row>
-    <row r="105" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B105" s="10"/>
       <c r="C105" s="10"/>
       <c r="D105" s="10"/>
       <c r="E105" s="22"/>
       <c r="F105" s="6"/>
     </row>
-    <row r="106" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B106" s="10"/>
       <c r="C106" s="10"/>
       <c r="D106" s="10"/>
       <c r="E106" s="22"/>
       <c r="F106" s="6"/>
     </row>
-    <row r="107" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B107" s="10"/>
       <c r="C107" s="10"/>
       <c r="D107" s="10"/>
       <c r="E107" s="22"/>
       <c r="F107" s="6"/>
     </row>
-    <row r="108" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B108" s="10"/>
       <c r="C108" s="10"/>
       <c r="D108" s="10"/>
       <c r="E108" s="22"/>
       <c r="F108" s="6"/>
     </row>
-    <row r="109" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B109" s="10"/>
       <c r="C109" s="10"/>
       <c r="D109" s="10"/>
       <c r="E109" s="22"/>
       <c r="F109" s="6"/>
     </row>
-    <row r="110" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B110" s="10"/>
       <c r="C110" s="10"/>
       <c r="D110" s="10"/>
       <c r="E110" s="22"/>
       <c r="F110" s="6"/>
     </row>
-    <row r="111" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B111" s="10"/>
       <c r="C111" s="10"/>
       <c r="D111" s="10"/>
@@ -6344,29 +6258,29 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F113939-C9CD-4F0E-99AE-A374EFC1A4A5}">
   <dimension ref="A1:I111"/>
-  <sheetFormatPr defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.03515625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.125" style="5" customWidth="1"/>
-    <col min="2" max="4" width="13.75" style="5" customWidth="1"/>
-    <col min="5" max="5" width="75.625" style="23" customWidth="1"/>
-    <col min="6" max="6" width="75.625" style="11" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="10.1484375" style="5" customWidth="1"/>
+    <col min="2" max="4" width="13.73828125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="75.6328125" style="23" customWidth="1"/>
+    <col min="6" max="6" width="75.6328125" style="11" customWidth="1"/>
+    <col min="7" max="16384" width="9.03515625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
+    <row r="1" spans="1:9" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
       <c r="G1" s="19"/>
       <c r="H1" s="19"/>
       <c r="I1" s="19"/>
     </row>
-    <row r="2" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -6374,7 +6288,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D2" s="18" t="s">
         <v>9</v>
@@ -6386,7 +6300,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>1</v>
       </c>
@@ -6396,7 +6310,7 @@
       <c r="E3" s="21"/>
       <c r="F3" s="7"/>
     </row>
-    <row r="4" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>2</v>
       </c>
@@ -6406,7 +6320,7 @@
       <c r="E4" s="21"/>
       <c r="F4" s="8"/>
     </row>
-    <row r="5" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>3</v>
       </c>
@@ -6416,7 +6330,7 @@
       <c r="E5" s="21"/>
       <c r="F5" s="7"/>
     </row>
-    <row r="6" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>4</v>
       </c>
@@ -6426,7 +6340,7 @@
       <c r="E6" s="21"/>
       <c r="F6" s="8"/>
     </row>
-    <row r="7" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>5</v>
       </c>
@@ -6436,7 +6350,7 @@
       <c r="E7" s="21"/>
       <c r="F7" s="7"/>
     </row>
-    <row r="8" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>6</v>
       </c>
@@ -6446,7 +6360,7 @@
       <c r="E8" s="21"/>
       <c r="F8" s="8"/>
     </row>
-    <row r="9" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>7</v>
       </c>
@@ -6456,7 +6370,7 @@
       <c r="E9" s="24"/>
       <c r="F9" s="7"/>
     </row>
-    <row r="10" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>8</v>
       </c>
@@ -6466,7 +6380,7 @@
       <c r="E10" s="21"/>
       <c r="F10" s="8"/>
     </row>
-    <row r="11" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>9</v>
       </c>
@@ -6476,7 +6390,7 @@
       <c r="E11" s="21"/>
       <c r="F11" s="7"/>
     </row>
-    <row r="12" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>10</v>
       </c>
@@ -6486,7 +6400,7 @@
       <c r="E12" s="21"/>
       <c r="F12" s="8"/>
     </row>
-    <row r="13" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>11</v>
       </c>
@@ -6496,7 +6410,7 @@
       <c r="E13" s="21"/>
       <c r="F13" s="7"/>
     </row>
-    <row r="14" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>12</v>
       </c>
@@ -6506,7 +6420,7 @@
       <c r="E14" s="21"/>
       <c r="F14" s="8"/>
     </row>
-    <row r="15" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>13</v>
       </c>
@@ -6516,7 +6430,7 @@
       <c r="E15" s="21"/>
       <c r="F15" s="7"/>
     </row>
-    <row r="16" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>14</v>
       </c>
@@ -6526,7 +6440,7 @@
       <c r="E16" s="21"/>
       <c r="F16" s="8"/>
     </row>
-    <row r="17" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>15</v>
       </c>
@@ -6536,7 +6450,7 @@
       <c r="E17" s="21"/>
       <c r="F17" s="7"/>
     </row>
-    <row r="18" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>16</v>
       </c>
@@ -6546,7 +6460,7 @@
       <c r="E18" s="21"/>
       <c r="F18" s="8"/>
     </row>
-    <row r="19" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>17</v>
       </c>
@@ -6556,7 +6470,7 @@
       <c r="E19" s="21"/>
       <c r="F19" s="7"/>
     </row>
-    <row r="20" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>18</v>
       </c>
@@ -6566,7 +6480,7 @@
       <c r="E20" s="21"/>
       <c r="F20" s="8"/>
     </row>
-    <row r="21" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>19</v>
       </c>
@@ -6576,7 +6490,7 @@
       <c r="E21" s="21"/>
       <c r="F21" s="8"/>
     </row>
-    <row r="22" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>20</v>
       </c>
@@ -6586,7 +6500,7 @@
       <c r="E22" s="21"/>
       <c r="F22" s="7"/>
     </row>
-    <row r="23" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>21</v>
       </c>
@@ -6596,7 +6510,7 @@
       <c r="E23" s="21"/>
       <c r="F23" s="8"/>
     </row>
-    <row r="24" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>22</v>
       </c>
@@ -6606,7 +6520,7 @@
       <c r="E24" s="21"/>
       <c r="F24" s="8"/>
     </row>
-    <row r="25" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>23</v>
       </c>
@@ -6616,7 +6530,7 @@
       <c r="E25" s="21"/>
       <c r="F25" s="7"/>
     </row>
-    <row r="26" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>24</v>
       </c>
@@ -6626,7 +6540,7 @@
       <c r="E26" s="21"/>
       <c r="F26" s="8"/>
     </row>
-    <row r="27" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>25</v>
       </c>
@@ -6636,7 +6550,7 @@
       <c r="E27" s="21"/>
       <c r="F27" s="8"/>
     </row>
-    <row r="28" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>26</v>
       </c>
@@ -6646,7 +6560,7 @@
       <c r="E28" s="21"/>
       <c r="F28" s="7"/>
     </row>
-    <row r="29" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>27</v>
       </c>
@@ -6656,7 +6570,7 @@
       <c r="E29" s="21"/>
       <c r="F29" s="8"/>
     </row>
-    <row r="30" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>28</v>
       </c>
@@ -6666,7 +6580,7 @@
       <c r="E30" s="21"/>
       <c r="F30" s="8"/>
     </row>
-    <row r="31" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>29</v>
       </c>
@@ -6676,7 +6590,7 @@
       <c r="E31" s="21"/>
       <c r="F31" s="7"/>
     </row>
-    <row r="32" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>30</v>
       </c>
@@ -6686,7 +6600,7 @@
       <c r="E32" s="21"/>
       <c r="F32" s="8"/>
     </row>
-    <row r="33" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>31</v>
       </c>
@@ -6696,7 +6610,7 @@
       <c r="E33" s="21"/>
       <c r="F33" s="8"/>
     </row>
-    <row r="34" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <v>32</v>
       </c>
@@ -6706,7 +6620,7 @@
       <c r="E34" s="21"/>
       <c r="F34" s="7"/>
     </row>
-    <row r="35" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>33</v>
       </c>
@@ -6716,7 +6630,7 @@
       <c r="E35" s="21"/>
       <c r="F35" s="8"/>
     </row>
-    <row r="36" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>34</v>
       </c>
@@ -6726,7 +6640,7 @@
       <c r="E36" s="21"/>
       <c r="F36" s="8"/>
     </row>
-    <row r="37" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>35</v>
       </c>
@@ -6736,7 +6650,7 @@
       <c r="E37" s="21"/>
       <c r="F37" s="7"/>
     </row>
-    <row r="38" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>36</v>
       </c>
@@ -6746,7 +6660,7 @@
       <c r="E38" s="21"/>
       <c r="F38" s="8"/>
     </row>
-    <row r="39" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>37</v>
       </c>
@@ -6756,7 +6670,7 @@
       <c r="E39" s="21"/>
       <c r="F39" s="8"/>
     </row>
-    <row r="40" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>38</v>
       </c>
@@ -6766,7 +6680,7 @@
       <c r="E40" s="21"/>
       <c r="F40" s="7"/>
     </row>
-    <row r="41" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>39</v>
       </c>
@@ -6776,7 +6690,7 @@
       <c r="E41" s="21"/>
       <c r="F41" s="8"/>
     </row>
-    <row r="42" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <v>40</v>
       </c>
@@ -6786,7 +6700,7 @@
       <c r="E42" s="21"/>
       <c r="F42" s="7"/>
     </row>
-    <row r="43" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>41</v>
       </c>
@@ -6796,7 +6710,7 @@
       <c r="E43" s="21"/>
       <c r="F43" s="8"/>
     </row>
-    <row r="44" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <v>42</v>
       </c>
@@ -6806,7 +6720,7 @@
       <c r="E44" s="21"/>
       <c r="F44" s="8"/>
     </row>
-    <row r="45" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>43</v>
       </c>
@@ -6816,7 +6730,7 @@
       <c r="E45" s="21"/>
       <c r="F45" s="7"/>
     </row>
-    <row r="46" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <v>44</v>
       </c>
@@ -6826,7 +6740,7 @@
       <c r="E46" s="21"/>
       <c r="F46" s="8"/>
     </row>
-    <row r="47" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <v>45</v>
       </c>
@@ -6836,7 +6750,7 @@
       <c r="E47" s="21"/>
       <c r="F47" s="8"/>
     </row>
-    <row r="48" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <v>46</v>
       </c>
@@ -6846,7 +6760,7 @@
       <c r="E48" s="21"/>
       <c r="F48" s="7"/>
     </row>
-    <row r="49" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>47</v>
       </c>
@@ -6856,7 +6770,7 @@
       <c r="E49" s="21"/>
       <c r="F49" s="8"/>
     </row>
-    <row r="50" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
         <v>48</v>
       </c>
@@ -6866,7 +6780,7 @@
       <c r="E50" s="21"/>
       <c r="F50" s="7"/>
     </row>
-    <row r="51" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <v>49</v>
       </c>
@@ -6876,7 +6790,7 @@
       <c r="E51" s="21"/>
       <c r="F51" s="8"/>
     </row>
-    <row r="52" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
         <v>50</v>
       </c>
@@ -6886,413 +6800,413 @@
       <c r="E52" s="21"/>
       <c r="F52" s="7"/>
     </row>
-    <row r="53" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="10"/>
       <c r="C53" s="10"/>
       <c r="D53" s="10"/>
       <c r="E53" s="22"/>
       <c r="F53" s="6"/>
     </row>
-    <row r="54" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="10"/>
       <c r="C54" s="10"/>
       <c r="D54" s="10"/>
       <c r="E54" s="22"/>
       <c r="F54" s="6"/>
     </row>
-    <row r="55" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="10"/>
       <c r="C55" s="10"/>
       <c r="D55" s="10"/>
       <c r="E55" s="22"/>
       <c r="F55" s="6"/>
     </row>
-    <row r="56" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="10"/>
       <c r="C56" s="10"/>
       <c r="D56" s="10"/>
       <c r="E56" s="22"/>
       <c r="F56" s="6"/>
     </row>
-    <row r="57" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="10"/>
       <c r="C57" s="10"/>
       <c r="D57" s="10"/>
       <c r="E57" s="22"/>
       <c r="F57" s="6"/>
     </row>
-    <row r="58" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="10"/>
       <c r="C58" s="10"/>
       <c r="D58" s="10"/>
       <c r="E58" s="22"/>
       <c r="F58" s="6"/>
     </row>
-    <row r="59" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="10"/>
       <c r="C59" s="10"/>
       <c r="D59" s="10"/>
       <c r="E59" s="22"/>
       <c r="F59" s="6"/>
     </row>
-    <row r="60" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="10"/>
       <c r="C60" s="10"/>
       <c r="D60" s="10"/>
       <c r="E60" s="22"/>
       <c r="F60" s="6"/>
     </row>
-    <row r="61" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="10"/>
       <c r="C61" s="10"/>
       <c r="D61" s="10"/>
       <c r="E61" s="22"/>
       <c r="F61" s="6"/>
     </row>
-    <row r="62" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="10"/>
       <c r="C62" s="10"/>
       <c r="D62" s="10"/>
       <c r="E62" s="22"/>
       <c r="F62" s="6"/>
     </row>
-    <row r="63" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="10"/>
       <c r="C63" s="10"/>
       <c r="D63" s="10"/>
       <c r="E63" s="22"/>
       <c r="F63" s="6"/>
     </row>
-    <row r="64" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B64" s="10"/>
       <c r="C64" s="10"/>
       <c r="D64" s="10"/>
       <c r="E64" s="22"/>
       <c r="F64" s="6"/>
     </row>
-    <row r="65" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="10"/>
       <c r="C65" s="10"/>
       <c r="D65" s="10"/>
       <c r="E65" s="22"/>
       <c r="F65" s="6"/>
     </row>
-    <row r="66" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="10"/>
       <c r="C66" s="10"/>
       <c r="D66" s="10"/>
       <c r="E66" s="22"/>
       <c r="F66" s="6"/>
     </row>
-    <row r="67" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="10"/>
       <c r="C67" s="10"/>
       <c r="D67" s="10"/>
       <c r="E67" s="22"/>
       <c r="F67" s="6"/>
     </row>
-    <row r="68" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="10"/>
       <c r="C68" s="10"/>
       <c r="D68" s="10"/>
       <c r="E68" s="22"/>
       <c r="F68" s="6"/>
     </row>
-    <row r="69" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B69" s="10"/>
       <c r="C69" s="10"/>
       <c r="D69" s="10"/>
       <c r="E69" s="22"/>
       <c r="F69" s="6"/>
     </row>
-    <row r="70" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="10"/>
       <c r="C70" s="10"/>
       <c r="D70" s="10"/>
       <c r="E70" s="22"/>
       <c r="F70" s="6"/>
     </row>
-    <row r="71" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="10"/>
       <c r="C71" s="10"/>
       <c r="D71" s="10"/>
       <c r="E71" s="22"/>
       <c r="F71" s="6"/>
     </row>
-    <row r="72" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B72" s="10"/>
       <c r="C72" s="10"/>
       <c r="D72" s="10"/>
       <c r="E72" s="22"/>
       <c r="F72" s="6"/>
     </row>
-    <row r="73" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B73" s="10"/>
       <c r="C73" s="10"/>
       <c r="D73" s="10"/>
       <c r="E73" s="22"/>
       <c r="F73" s="6"/>
     </row>
-    <row r="74" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" s="10"/>
       <c r="C74" s="10"/>
       <c r="D74" s="10"/>
       <c r="E74" s="22"/>
       <c r="F74" s="6"/>
     </row>
-    <row r="75" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B75" s="10"/>
       <c r="C75" s="10"/>
       <c r="D75" s="10"/>
       <c r="E75" s="22"/>
       <c r="F75" s="6"/>
     </row>
-    <row r="76" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B76" s="10"/>
       <c r="C76" s="10"/>
       <c r="D76" s="10"/>
       <c r="E76" s="22"/>
       <c r="F76" s="6"/>
     </row>
-    <row r="77" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="10"/>
       <c r="C77" s="10"/>
       <c r="D77" s="10"/>
       <c r="E77" s="22"/>
       <c r="F77" s="6"/>
     </row>
-    <row r="78" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B78" s="10"/>
       <c r="C78" s="10"/>
       <c r="D78" s="10"/>
       <c r="E78" s="22"/>
       <c r="F78" s="6"/>
     </row>
-    <row r="79" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B79" s="10"/>
       <c r="C79" s="10"/>
       <c r="D79" s="10"/>
       <c r="E79" s="22"/>
       <c r="F79" s="6"/>
     </row>
-    <row r="80" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B80" s="10"/>
       <c r="C80" s="10"/>
       <c r="D80" s="10"/>
       <c r="E80" s="22"/>
       <c r="F80" s="6"/>
     </row>
-    <row r="81" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B81" s="10"/>
       <c r="C81" s="10"/>
       <c r="D81" s="10"/>
       <c r="E81" s="22"/>
       <c r="F81" s="6"/>
     </row>
-    <row r="82" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" s="10"/>
       <c r="C82" s="10"/>
       <c r="D82" s="10"/>
       <c r="E82" s="22"/>
       <c r="F82" s="6"/>
     </row>
-    <row r="83" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B83" s="10"/>
       <c r="C83" s="10"/>
       <c r="D83" s="10"/>
       <c r="E83" s="22"/>
       <c r="F83" s="6"/>
     </row>
-    <row r="84" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B84" s="10"/>
       <c r="C84" s="10"/>
       <c r="D84" s="10"/>
       <c r="E84" s="22"/>
       <c r="F84" s="6"/>
     </row>
-    <row r="85" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B85" s="10"/>
       <c r="C85" s="10"/>
       <c r="D85" s="10"/>
       <c r="E85" s="22"/>
       <c r="F85" s="6"/>
     </row>
-    <row r="86" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B86" s="10"/>
       <c r="C86" s="10"/>
       <c r="D86" s="10"/>
       <c r="E86" s="22"/>
       <c r="F86" s="6"/>
     </row>
-    <row r="87" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B87" s="10"/>
       <c r="C87" s="10"/>
       <c r="D87" s="10"/>
       <c r="E87" s="22"/>
       <c r="F87" s="6"/>
     </row>
-    <row r="88" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B88" s="10"/>
       <c r="C88" s="10"/>
       <c r="D88" s="10"/>
       <c r="E88" s="22"/>
       <c r="F88" s="6"/>
     </row>
-    <row r="89" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B89" s="10"/>
       <c r="C89" s="10"/>
       <c r="D89" s="10"/>
       <c r="E89" s="22"/>
       <c r="F89" s="6"/>
     </row>
-    <row r="90" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B90" s="10"/>
       <c r="C90" s="10"/>
       <c r="D90" s="10"/>
       <c r="E90" s="22"/>
       <c r="F90" s="6"/>
     </row>
-    <row r="91" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B91" s="10"/>
       <c r="C91" s="10"/>
       <c r="D91" s="10"/>
       <c r="E91" s="22"/>
       <c r="F91" s="6"/>
     </row>
-    <row r="92" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B92" s="10"/>
       <c r="C92" s="10"/>
       <c r="D92" s="10"/>
       <c r="E92" s="22"/>
       <c r="F92" s="6"/>
     </row>
-    <row r="93" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B93" s="10"/>
       <c r="C93" s="10"/>
       <c r="D93" s="10"/>
       <c r="E93" s="22"/>
       <c r="F93" s="6"/>
     </row>
-    <row r="94" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B94" s="10"/>
       <c r="C94" s="10"/>
       <c r="D94" s="10"/>
       <c r="E94" s="22"/>
       <c r="F94" s="6"/>
     </row>
-    <row r="95" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B95" s="10"/>
       <c r="C95" s="10"/>
       <c r="D95" s="10"/>
       <c r="E95" s="22"/>
       <c r="F95" s="6"/>
     </row>
-    <row r="96" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B96" s="10"/>
       <c r="C96" s="10"/>
       <c r="D96" s="10"/>
       <c r="E96" s="22"/>
       <c r="F96" s="6"/>
     </row>
-    <row r="97" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B97" s="10"/>
       <c r="C97" s="10"/>
       <c r="D97" s="10"/>
       <c r="E97" s="22"/>
       <c r="F97" s="6"/>
     </row>
-    <row r="98" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B98" s="10"/>
       <c r="C98" s="10"/>
       <c r="D98" s="10"/>
       <c r="E98" s="22"/>
       <c r="F98" s="6"/>
     </row>
-    <row r="99" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B99" s="10"/>
       <c r="C99" s="10"/>
       <c r="D99" s="10"/>
       <c r="E99" s="22"/>
       <c r="F99" s="6"/>
     </row>
-    <row r="100" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B100" s="10"/>
       <c r="C100" s="10"/>
       <c r="D100" s="10"/>
       <c r="E100" s="22"/>
       <c r="F100" s="6"/>
     </row>
-    <row r="101" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B101" s="10"/>
       <c r="C101" s="10"/>
       <c r="D101" s="10"/>
       <c r="E101" s="22"/>
       <c r="F101" s="6"/>
     </row>
-    <row r="102" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B102" s="10"/>
       <c r="C102" s="10"/>
       <c r="D102" s="10"/>
       <c r="E102" s="22"/>
       <c r="F102" s="6"/>
     </row>
-    <row r="103" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B103" s="10"/>
       <c r="C103" s="10"/>
       <c r="D103" s="10"/>
       <c r="E103" s="22"/>
       <c r="F103" s="6"/>
     </row>
-    <row r="104" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B104" s="10"/>
       <c r="C104" s="10"/>
       <c r="D104" s="10"/>
       <c r="E104" s="22"/>
       <c r="F104" s="6"/>
     </row>
-    <row r="105" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B105" s="10"/>
       <c r="C105" s="10"/>
       <c r="D105" s="10"/>
       <c r="E105" s="22"/>
       <c r="F105" s="6"/>
     </row>
-    <row r="106" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B106" s="10"/>
       <c r="C106" s="10"/>
       <c r="D106" s="10"/>
       <c r="E106" s="22"/>
       <c r="F106" s="6"/>
     </row>
-    <row r="107" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B107" s="10"/>
       <c r="C107" s="10"/>
       <c r="D107" s="10"/>
       <c r="E107" s="22"/>
       <c r="F107" s="6"/>
     </row>
-    <row r="108" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B108" s="10"/>
       <c r="C108" s="10"/>
       <c r="D108" s="10"/>
       <c r="E108" s="22"/>
       <c r="F108" s="6"/>
     </row>
-    <row r="109" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B109" s="10"/>
       <c r="C109" s="10"/>
       <c r="D109" s="10"/>
       <c r="E109" s="22"/>
       <c r="F109" s="6"/>
     </row>
-    <row r="110" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B110" s="10"/>
       <c r="C110" s="10"/>
       <c r="D110" s="10"/>
       <c r="E110" s="22"/>
       <c r="F110" s="6"/>
     </row>
-    <row r="111" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B111" s="10"/>
       <c r="C111" s="10"/>
       <c r="D111" s="10"/>
